--- a/portfolio_tracker.xlsx
+++ b/portfolio_tracker.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexr\AlgoTester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C683590-86FC-469F-8E7B-161CDC0113A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E87E9C9-0997-45AB-A9B1-9ED6CE92E585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$E$24</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,48 +39,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="12">
   <si>
     <t>date</t>
   </si>
   <si>
-    <t>SPY_price</t>
-  </si>
-  <si>
-    <t>TLT_price</t>
-  </si>
-  <si>
-    <t>GLD_price</t>
-  </si>
-  <si>
-    <t>SHV_price</t>
-  </si>
-  <si>
-    <t>capital_injection</t>
-  </si>
-  <si>
-    <t>SPY_size</t>
-  </si>
-  <si>
-    <t>TLT_size</t>
-  </si>
-  <si>
-    <t>GLD_size</t>
-  </si>
-  <si>
-    <t>SHV_size</t>
-  </si>
-  <si>
-    <t>SPY_fees</t>
-  </si>
-  <si>
-    <t>TLT_fees</t>
-  </si>
-  <si>
-    <t>GLD_fees</t>
-  </si>
-  <si>
-    <t>SHV_fees</t>
+    <t>quantity</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>fees</t>
+  </si>
+  <si>
+    <t>CASH</t>
+  </si>
+  <si>
+    <t>SPY</t>
+  </si>
+  <si>
+    <t>GLD</t>
+  </si>
+  <si>
+    <t>SHV</t>
+  </si>
+  <si>
+    <t>TLT</t>
+  </si>
+  <si>
+    <t>PPLT</t>
+  </si>
+  <si>
+    <t>URA</t>
+  </si>
+  <si>
+    <t>ticker</t>
   </si>
 </sst>
 </file>
@@ -124,11 +121,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -409,115 +408,497 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="13.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EBC9900-0457-4E2A-A65B-407C2F1035D0}">
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.21875" style="1"/>
-    <col min="2" max="2" width="14.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="13.21875" style="2"/>
-    <col min="7" max="8" width="13.21875" style="3"/>
-    <col min="9" max="9" width="13.21875" style="2"/>
-    <col min="10" max="11" width="13.21875" style="3"/>
-    <col min="12" max="12" width="13.21875" style="2"/>
-    <col min="13" max="14" width="13.21875" style="3"/>
-    <col min="15" max="21" width="13.21875" style="2"/>
-    <col min="22" max="22" width="16" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="13.21875" style="2"/>
+    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="3" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="3" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45748</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="4">
         <v>63886</v>
       </c>
-      <c r="C2" s="2">
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>45748</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="5">
         <v>9</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D3" s="3">
         <v>557.48</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E3" s="3">
         <v>1.01</v>
       </c>
-      <c r="F2" s="2">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>45748</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="5">
+        <v>65</v>
+      </c>
+      <c r="D4" s="3">
+        <v>288.64</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>45748</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="5">
+        <v>364</v>
+      </c>
+      <c r="D5" s="3">
+        <v>110.1</v>
+      </c>
+      <c r="E5" s="3">
+        <v>2.44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>45753</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1500</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
         <v>0</v>
       </c>
-      <c r="G2" s="3">
-        <v>91.25</v>
-      </c>
-      <c r="H2" s="3">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>45754</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="5">
+        <v>35</v>
+      </c>
+      <c r="D7" s="2">
+        <v>110.2</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>45754</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-45</v>
+      </c>
+      <c r="D8" s="2">
+        <v>278.69</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>45754</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="5">
+        <v>91</v>
+      </c>
+      <c r="D9" s="2">
+        <v>91.85</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>45761</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-7</v>
+      </c>
+      <c r="D10" s="2">
+        <v>544</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>45761</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-91</v>
+      </c>
+      <c r="D11" s="2">
+        <v>87.42</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>45761</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="5">
+        <v>76</v>
+      </c>
+      <c r="D12" s="2">
+        <v>295.41000000000003</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>45761</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-86</v>
+      </c>
+      <c r="D13" s="2">
+        <v>110.25</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>45762</v>
+      </c>
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1500</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2">
         <v>0</v>
       </c>
-      <c r="I2" s="2">
-        <v>65</v>
-      </c>
-      <c r="J2" s="3">
-        <v>288.64</v>
-      </c>
-      <c r="K2" s="3">
-        <v>0.79</v>
-      </c>
-      <c r="L2" s="2">
-        <v>364</v>
-      </c>
-      <c r="M2" s="3">
-        <v>110.1</v>
-      </c>
-      <c r="N2" s="3">
-        <v>2.44</v>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>45768</v>
+      </c>
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="5">
+        <v>3</v>
+      </c>
+      <c r="D15" s="2">
+        <v>521.11</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>45768</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="5">
+        <v>59</v>
+      </c>
+      <c r="D16" s="2">
+        <v>314.95999999999998</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>45768</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-63</v>
+      </c>
+      <c r="D17" s="2">
+        <v>110.35</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>45768</v>
+      </c>
+      <c r="B18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="5">
+        <v>11</v>
+      </c>
+      <c r="D18" s="2">
+        <v>88.45</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>45768</v>
+      </c>
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="5">
+        <v>45</v>
+      </c>
+      <c r="D19" s="2">
+        <v>22.95</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>45768</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-100</v>
+      </c>
+      <c r="D20" s="2">
+        <v>110.34</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>45775</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-143</v>
+      </c>
+      <c r="D21" s="2">
+        <v>110.43</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>45775</v>
+      </c>
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>153</v>
+      </c>
+      <c r="D22" s="2">
+        <v>88.66</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>45775</v>
+      </c>
+      <c r="B23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="5">
+        <v>16</v>
+      </c>
+      <c r="D23" s="2">
+        <v>551.34</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>45775</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-23</v>
+      </c>
+      <c r="D24" s="2">
+        <v>304.14999999999998</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>45782</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-106</v>
+      </c>
+      <c r="D25" s="2">
+        <v>305.95</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>45782</v>
+      </c>
+      <c r="B26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-153</v>
+      </c>
+      <c r="D26" s="2">
+        <v>87.36</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>45782</v>
+      </c>
+      <c r="B27" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-10</v>
+      </c>
+      <c r="D27" s="2">
+        <v>562.48</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>45782</v>
+      </c>
+      <c r="B28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="5">
+        <v>475</v>
+      </c>
+      <c r="D28" s="2">
+        <v>110.12</v>
+      </c>
+      <c r="E28" s="2">
+        <v>2.71</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E24" xr:uid="{1EBC9900-0457-4E2A-A65B-407C2F1035D0}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E24">
+      <sortCondition ref="A1:A24"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/portfolio_tracker.xlsx
+++ b/portfolio_tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexr\AlgoTester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E87E9C9-0997-45AB-A9B1-9ED6CE92E585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9A9FC72-CA87-40D2-A34F-9D7796F59F1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="12">
   <si>
     <t>date</t>
   </si>
@@ -409,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EBC9900-0457-4E2A-A65B-407C2F1035D0}">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
@@ -893,6 +893,23 @@
         <v>2.71</v>
       </c>
     </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>45784</v>
+      </c>
+      <c r="B29" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" s="5">
+        <v>1550</v>
+      </c>
+      <c r="D29" s="2">
+        <v>1</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E24" xr:uid="{1EBC9900-0457-4E2A-A65B-407C2F1035D0}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E24">

--- a/portfolio_tracker.xlsx
+++ b/portfolio_tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexr\AlgoTester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9A9FC72-CA87-40D2-A34F-9D7796F59F1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC88FA25-CA53-410C-84B7-F9C205B338DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="18">
   <si>
     <t>date</t>
   </si>
@@ -75,6 +75,24 @@
   </si>
   <si>
     <t>ticker</t>
+  </si>
+  <si>
+    <t>IB01.L</t>
+  </si>
+  <si>
+    <t>USO</t>
+  </si>
+  <si>
+    <t>IBIT</t>
+  </si>
+  <si>
+    <t>LQD</t>
+  </si>
+  <si>
+    <t>EEM</t>
+  </si>
+  <si>
+    <t>DBA</t>
   </si>
 </sst>
 </file>
@@ -409,7 +427,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EBC9900-0457-4E2A-A65B-407C2F1035D0}">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
@@ -910,6 +928,313 @@
         <v>0</v>
       </c>
     </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>45804</v>
+      </c>
+      <c r="B30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-13</v>
+      </c>
+      <c r="D30" s="2">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>45804</v>
+      </c>
+      <c r="B31" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="5">
+        <v>427</v>
+      </c>
+      <c r="D31" s="2">
+        <v>115.93</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>45804</v>
+      </c>
+      <c r="B32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="5">
+        <v>2</v>
+      </c>
+      <c r="D32" s="2">
+        <v>303.83999999999997</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>45804</v>
+      </c>
+      <c r="B33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="5">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2">
+        <v>586.14</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>45804</v>
+      </c>
+      <c r="B34" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-482</v>
+      </c>
+      <c r="D34" s="2">
+        <v>110.39</v>
+      </c>
+      <c r="E34" s="2">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>45824</v>
+      </c>
+      <c r="B35" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" s="5">
+        <v>4689</v>
+      </c>
+      <c r="D35" s="2">
+        <v>1</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>45824</v>
+      </c>
+      <c r="B36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" s="5">
+        <v>1</v>
+      </c>
+      <c r="D36" s="2">
+        <v>79.05</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>45824</v>
+      </c>
+      <c r="B37" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="5">
+        <v>25</v>
+      </c>
+      <c r="D37" s="2">
+        <v>60.61</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>45824</v>
+      </c>
+      <c r="B38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" s="5">
+        <v>486</v>
+      </c>
+      <c r="D38" s="2">
+        <v>107.8</v>
+      </c>
+      <c r="E38" s="2">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>45824</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="5">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2">
+        <v>47.2</v>
+      </c>
+      <c r="E39" s="2">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>45824</v>
+      </c>
+      <c r="B40" t="s">
+        <v>17</v>
+      </c>
+      <c r="C40" s="5">
+        <v>500</v>
+      </c>
+      <c r="D40" s="2">
+        <v>26.98</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>45824</v>
+      </c>
+      <c r="B41" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2">
+        <v>314.77</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0.39</v>
+      </c>
+      <c r="H41" s="2"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>45824</v>
+      </c>
+      <c r="B42" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-427</v>
+      </c>
+      <c r="D42" s="2">
+        <v>116.14</v>
+      </c>
+      <c r="E42" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>45824</v>
+      </c>
+      <c r="B43" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-14</v>
+      </c>
+      <c r="D43" s="2">
+        <v>600.34</v>
+      </c>
+      <c r="E43" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>45831</v>
+      </c>
+      <c r="B44" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="5">
+        <v>90</v>
+      </c>
+      <c r="D44" s="2">
+        <v>116.24</v>
+      </c>
+      <c r="E44" s="2">
+        <v>5.72</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>45831</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-61</v>
+      </c>
+      <c r="D45" s="2">
+        <v>46.25</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>45831</v>
+      </c>
+      <c r="B46" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" s="5">
+        <v>202</v>
+      </c>
+      <c r="D46" s="2">
+        <v>57.47</v>
+      </c>
+      <c r="E46" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>45831</v>
+      </c>
+      <c r="B47" t="s">
+        <v>15</v>
+      </c>
+      <c r="C47" s="5">
+        <v>-263</v>
+      </c>
+      <c r="D47" s="2">
+        <v>108.39</v>
+      </c>
+      <c r="E47" s="2">
+        <v>1.26</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E24" xr:uid="{1EBC9900-0457-4E2A-A65B-407C2F1035D0}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E24">

--- a/portfolio_tracker.xlsx
+++ b/portfolio_tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexr\AlgoTester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC88FA25-CA53-410C-84B7-F9C205B338DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B6964AD-1156-4475-B86F-F58A2740A256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$E$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$E$97</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="34">
   <si>
     <t>date</t>
   </si>
@@ -93,6 +93,54 @@
   </si>
   <si>
     <t>DBA</t>
+  </si>
+  <si>
+    <t>CPER</t>
+  </si>
+  <si>
+    <t>UUUU</t>
+  </si>
+  <si>
+    <t>UPRO</t>
+  </si>
+  <si>
+    <t>ABAT</t>
+  </si>
+  <si>
+    <t>TMF</t>
+  </si>
+  <si>
+    <t>CSPX.L</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>LEU</t>
+  </si>
+  <si>
+    <t>BWXT</t>
+  </si>
+  <si>
+    <t>OKLO</t>
+  </si>
+  <si>
+    <t>SMR</t>
+  </si>
+  <si>
+    <t>GOOG</t>
+  </si>
+  <si>
+    <t>MSFT</t>
+  </si>
+  <si>
+    <t>HOOD</t>
+  </si>
+  <si>
+    <t>SHNY</t>
+  </si>
+  <si>
+    <t>ETHA</t>
   </si>
 </sst>
 </file>
@@ -427,10 +475,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EBC9900-0457-4E2A-A65B-407C2F1035D0}">
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H158"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.5546875" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="8.88671875" style="2"/>
   </cols>
@@ -1235,8 +1283,1895 @@
         <v>1.26</v>
       </c>
     </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>45838</v>
+      </c>
+      <c r="B48" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" s="5">
+        <v>-305</v>
+      </c>
+      <c r="D48" s="2">
+        <v>61.27</v>
+      </c>
+      <c r="E48" s="2">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>45838</v>
+      </c>
+      <c r="B49" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" s="5">
+        <v>432</v>
+      </c>
+      <c r="D49" s="2">
+        <v>26.25</v>
+      </c>
+      <c r="E49" s="2">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>45838</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" s="5">
+        <v>-54</v>
+      </c>
+      <c r="D50" s="2">
+        <v>48.02</v>
+      </c>
+      <c r="E50" s="2">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>45838</v>
+      </c>
+      <c r="B51" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="5">
+        <v>-14</v>
+      </c>
+      <c r="D51" s="2">
+        <v>302.33</v>
+      </c>
+      <c r="E51" s="2">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>45838</v>
+      </c>
+      <c r="B52" t="s">
+        <v>15</v>
+      </c>
+      <c r="C52" s="5">
+        <v>190</v>
+      </c>
+      <c r="D52" s="2">
+        <v>109.3</v>
+      </c>
+      <c r="E52" s="2">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>45838</v>
+      </c>
+      <c r="B53" t="s">
+        <v>9</v>
+      </c>
+      <c r="C53" s="5">
+        <v>-47</v>
+      </c>
+      <c r="D53" s="2">
+        <v>122.61</v>
+      </c>
+      <c r="E53" s="2">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>45838</v>
+      </c>
+      <c r="B54" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54" s="5">
+        <v>14</v>
+      </c>
+      <c r="D54" s="2">
+        <v>617.42999999999995</v>
+      </c>
+      <c r="E54" s="2">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>45838</v>
+      </c>
+      <c r="B55" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="5">
+        <v>-71</v>
+      </c>
+      <c r="D55" s="2">
+        <v>38.75</v>
+      </c>
+      <c r="E55" s="2">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>45838</v>
+      </c>
+      <c r="B56" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" s="5">
+        <v>110</v>
+      </c>
+      <c r="D56" s="2">
+        <v>73.48</v>
+      </c>
+      <c r="E56" s="2">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>45852</v>
+      </c>
+      <c r="B57" t="s">
+        <v>4</v>
+      </c>
+      <c r="C57" s="5">
+        <v>2336</v>
+      </c>
+      <c r="D57" s="2">
+        <v>1</v>
+      </c>
+      <c r="E57" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>45852</v>
+      </c>
+      <c r="B58" t="s">
+        <v>14</v>
+      </c>
+      <c r="C58" s="5">
+        <v>82</v>
+      </c>
+      <c r="D58" s="2">
+        <v>69.2</v>
+      </c>
+      <c r="E58" s="2">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>45852</v>
+      </c>
+      <c r="B59" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="5">
+        <v>60</v>
+      </c>
+      <c r="D59" s="2">
+        <v>309.12</v>
+      </c>
+      <c r="E59" s="2">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>45852</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" s="5">
+        <v>495</v>
+      </c>
+      <c r="D60" s="2">
+        <v>48.27</v>
+      </c>
+      <c r="E60" s="2">
+        <v>2.2799999999999998</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>45852</v>
+      </c>
+      <c r="B61" t="s">
+        <v>5</v>
+      </c>
+      <c r="C61" s="5">
+        <v>-18</v>
+      </c>
+      <c r="D61" s="2">
+        <v>623.20000000000005</v>
+      </c>
+      <c r="E61" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>45852</v>
+      </c>
+      <c r="B62" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="5">
+        <v>-111</v>
+      </c>
+      <c r="D62" s="2">
+        <v>77.27</v>
+      </c>
+      <c r="E62" s="2">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>45852</v>
+      </c>
+      <c r="B63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="5">
+        <v>34</v>
+      </c>
+      <c r="D63" s="2">
+        <v>34.04</v>
+      </c>
+      <c r="E63" s="2">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>45852</v>
+      </c>
+      <c r="B64" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" s="5">
+        <v>70</v>
+      </c>
+      <c r="D64" s="2">
+        <v>37.6</v>
+      </c>
+      <c r="E64" s="2">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>45852</v>
+      </c>
+      <c r="B65" t="s">
+        <v>17</v>
+      </c>
+      <c r="C65" s="5">
+        <v>-932</v>
+      </c>
+      <c r="D65" s="2">
+        <v>25.95</v>
+      </c>
+      <c r="E65" s="2">
+        <v>4.46</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>45852</v>
+      </c>
+      <c r="B66" t="s">
+        <v>9</v>
+      </c>
+      <c r="C66" s="5">
+        <v>45</v>
+      </c>
+      <c r="D66" s="2">
+        <v>125</v>
+      </c>
+      <c r="E66" s="2">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>45852</v>
+      </c>
+      <c r="B67" t="s">
+        <v>15</v>
+      </c>
+      <c r="C67" s="5">
+        <v>-90</v>
+      </c>
+      <c r="D67" s="2">
+        <v>108.02</v>
+      </c>
+      <c r="E67" s="2">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>45859</v>
+      </c>
+      <c r="B68" t="s">
+        <v>12</v>
+      </c>
+      <c r="C68" s="5">
+        <v>-50</v>
+      </c>
+      <c r="D68" s="2">
+        <v>116.6</v>
+      </c>
+      <c r="E68" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>45859</v>
+      </c>
+      <c r="B69" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" s="5">
+        <v>6</v>
+      </c>
+      <c r="D69" s="2">
+        <v>41.6</v>
+      </c>
+      <c r="E69" s="2">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>45859</v>
+      </c>
+      <c r="B70" t="s">
+        <v>19</v>
+      </c>
+      <c r="C70" s="5">
+        <v>164</v>
+      </c>
+      <c r="D70" s="2">
+        <v>9.4499999999999993</v>
+      </c>
+      <c r="E70" s="2">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>45859</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" s="5">
+        <v>-142</v>
+      </c>
+      <c r="D71" s="2">
+        <v>49.33</v>
+      </c>
+      <c r="E71" s="2">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>45859</v>
+      </c>
+      <c r="B72" t="s">
+        <v>15</v>
+      </c>
+      <c r="C72" s="5">
+        <v>-159</v>
+      </c>
+      <c r="D72" s="2">
+        <v>108.86</v>
+      </c>
+      <c r="E72" s="2">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>45859</v>
+      </c>
+      <c r="B73" t="s">
+        <v>9</v>
+      </c>
+      <c r="C73" s="5">
+        <v>2</v>
+      </c>
+      <c r="D73" s="2">
+        <v>132.76</v>
+      </c>
+      <c r="E73" s="2">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>45859</v>
+      </c>
+      <c r="B74" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="5">
+        <v>-18</v>
+      </c>
+      <c r="D74" s="2">
+        <v>311.88</v>
+      </c>
+      <c r="E74" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>45859</v>
+      </c>
+      <c r="B75" t="s">
+        <v>20</v>
+      </c>
+      <c r="C75" s="5">
+        <v>108</v>
+      </c>
+      <c r="D75" s="2">
+        <v>95.67</v>
+      </c>
+      <c r="E75" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>45859</v>
+      </c>
+      <c r="B76" t="s">
+        <v>5</v>
+      </c>
+      <c r="C76" s="5">
+        <v>7</v>
+      </c>
+      <c r="D76" s="2">
+        <v>628.74</v>
+      </c>
+      <c r="E76" s="2">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>45859</v>
+      </c>
+      <c r="B77" t="s">
+        <v>21</v>
+      </c>
+      <c r="C77" s="5">
+        <v>643</v>
+      </c>
+      <c r="D77" s="2">
+        <v>2.74</v>
+      </c>
+      <c r="E77" s="2">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>45866</v>
+      </c>
+      <c r="B78" t="s">
+        <v>21</v>
+      </c>
+      <c r="C78" s="5">
+        <v>-321</v>
+      </c>
+      <c r="D78" s="2">
+        <v>3</v>
+      </c>
+      <c r="E78" s="2">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>45866</v>
+      </c>
+      <c r="B79" t="s">
+        <v>5</v>
+      </c>
+      <c r="C79" s="5">
+        <v>4</v>
+      </c>
+      <c r="D79" s="2">
+        <v>637.49</v>
+      </c>
+      <c r="E79" s="2">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
+        <v>45866</v>
+      </c>
+      <c r="B80" t="s">
+        <v>14</v>
+      </c>
+      <c r="C80" s="5">
+        <v>95</v>
+      </c>
+      <c r="D80" s="2">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="E80" s="2">
+        <v>0.56000000000000005</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
+        <v>45866</v>
+      </c>
+      <c r="B81" t="s">
+        <v>8</v>
+      </c>
+      <c r="C81" s="5">
+        <v>52</v>
+      </c>
+      <c r="D81" s="2">
+        <v>86</v>
+      </c>
+      <c r="E81" s="2">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <v>45866</v>
+      </c>
+      <c r="B82" t="s">
+        <v>15</v>
+      </c>
+      <c r="C82" s="5">
+        <v>-131</v>
+      </c>
+      <c r="D82" s="2">
+        <v>108.86</v>
+      </c>
+      <c r="E82" s="2">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>45866</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" s="5">
+        <v>211</v>
+      </c>
+      <c r="D83" s="2">
+        <v>49.31</v>
+      </c>
+      <c r="E83" s="2">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <v>45866</v>
+      </c>
+      <c r="B84" t="s">
+        <v>19</v>
+      </c>
+      <c r="C84" s="5">
+        <v>-64</v>
+      </c>
+      <c r="D84" s="2">
+        <v>10.3</v>
+      </c>
+      <c r="E84" s="2">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A85" s="1">
+        <v>45866</v>
+      </c>
+      <c r="B85" t="s">
+        <v>22</v>
+      </c>
+      <c r="C85" s="5">
+        <v>64</v>
+      </c>
+      <c r="D85" s="2">
+        <v>36.28</v>
+      </c>
+      <c r="E85" s="2">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <v>45866</v>
+      </c>
+      <c r="B86" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="5">
+        <v>-53</v>
+      </c>
+      <c r="D86" s="2">
+        <v>306.44</v>
+      </c>
+      <c r="E86" s="2">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>45866</v>
+      </c>
+      <c r="B87" t="s">
+        <v>10</v>
+      </c>
+      <c r="C87" s="5">
+        <v>-10</v>
+      </c>
+      <c r="D87" s="2">
+        <v>41.57</v>
+      </c>
+      <c r="E87" s="2">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <v>45866</v>
+      </c>
+      <c r="B88" t="s">
+        <v>9</v>
+      </c>
+      <c r="C88" s="5">
+        <v>-3</v>
+      </c>
+      <c r="D88" s="2">
+        <v>127.87</v>
+      </c>
+      <c r="E88" s="2">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
+        <v>45866</v>
+      </c>
+      <c r="B89" t="s">
+        <v>20</v>
+      </c>
+      <c r="C89" s="5">
+        <v>-18</v>
+      </c>
+      <c r="D89" s="2">
+        <v>99.51</v>
+      </c>
+      <c r="E89" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90" s="1">
+        <v>45866</v>
+      </c>
+      <c r="B90" t="s">
+        <v>12</v>
+      </c>
+      <c r="C90" s="5">
+        <v>112</v>
+      </c>
+      <c r="D90" s="2">
+        <v>116.7</v>
+      </c>
+      <c r="E90" s="2">
+        <v>7.85</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A91" s="1">
+        <v>45873</v>
+      </c>
+      <c r="B91" t="s">
+        <v>21</v>
+      </c>
+      <c r="C91" s="5">
+        <v>-322</v>
+      </c>
+      <c r="D91" s="2">
+        <v>2.37</v>
+      </c>
+      <c r="E91" s="2">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" s="1">
+        <v>45873</v>
+      </c>
+      <c r="B92" t="s">
+        <v>8</v>
+      </c>
+      <c r="C92" s="5">
+        <v>52</v>
+      </c>
+      <c r="D92" s="2">
+        <v>87.95</v>
+      </c>
+      <c r="E92" s="2">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
+        <v>45873</v>
+      </c>
+      <c r="B93" t="s">
+        <v>18</v>
+      </c>
+      <c r="C93" s="5">
+        <v>-34</v>
+      </c>
+      <c r="D93" s="2">
+        <v>27.67</v>
+      </c>
+      <c r="E93" s="2">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <v>45873</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" s="5">
+        <v>-230</v>
+      </c>
+      <c r="D94" s="2">
+        <v>48.74</v>
+      </c>
+      <c r="E94" s="2">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" s="1">
+        <v>45873</v>
+      </c>
+      <c r="B95" t="s">
+        <v>15</v>
+      </c>
+      <c r="C95" s="5">
+        <v>50</v>
+      </c>
+      <c r="D95" s="2">
+        <v>109.78</v>
+      </c>
+      <c r="E95" s="2">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <v>45873</v>
+      </c>
+      <c r="B96" t="s">
+        <v>9</v>
+      </c>
+      <c r="C96" s="5">
+        <v>-8</v>
+      </c>
+      <c r="D96" s="2">
+        <v>121.04</v>
+      </c>
+      <c r="E96" s="2">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>45873</v>
+      </c>
+      <c r="B97" t="s">
+        <v>19</v>
+      </c>
+      <c r="C97" s="5">
+        <v>-100</v>
+      </c>
+      <c r="D97" s="2">
+        <v>8.89</v>
+      </c>
+      <c r="E97" s="2">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>45894</v>
+      </c>
+      <c r="B98" t="s">
+        <v>8</v>
+      </c>
+      <c r="C98" s="5">
+        <v>4</v>
+      </c>
+      <c r="D98" s="2">
+        <v>86.73</v>
+      </c>
+      <c r="E98" s="2">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>45894</v>
+      </c>
+      <c r="B99" t="s">
+        <v>14</v>
+      </c>
+      <c r="C99" s="5">
+        <v>-18</v>
+      </c>
+      <c r="D99" s="2">
+        <v>63.46</v>
+      </c>
+      <c r="E99" s="2">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>45894</v>
+      </c>
+      <c r="B100" t="s">
+        <v>5</v>
+      </c>
+      <c r="C100" s="5">
+        <v>-13</v>
+      </c>
+      <c r="D100" s="2">
+        <v>644</v>
+      </c>
+      <c r="E100" s="2">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A101" s="1">
+        <v>45894</v>
+      </c>
+      <c r="B101" t="s">
+        <v>20</v>
+      </c>
+      <c r="C101" s="5">
+        <v>-35</v>
+      </c>
+      <c r="D101" s="2">
+        <v>101.39</v>
+      </c>
+      <c r="E101" s="2">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>45894</v>
+      </c>
+      <c r="B102" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" s="5">
+        <v>7</v>
+      </c>
+      <c r="D102" s="2">
+        <v>309.67</v>
+      </c>
+      <c r="E102" s="2">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>45894</v>
+      </c>
+      <c r="B103" t="s">
+        <v>22</v>
+      </c>
+      <c r="C103" s="5">
+        <v>-64</v>
+      </c>
+      <c r="D103" s="2">
+        <v>37.25</v>
+      </c>
+      <c r="E103" s="2">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>45894</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" s="5">
+        <v>-62</v>
+      </c>
+      <c r="D104" s="2">
+        <v>50.53</v>
+      </c>
+      <c r="E104" s="2">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>45894</v>
+      </c>
+      <c r="B105" t="s">
+        <v>15</v>
+      </c>
+      <c r="C105" s="5">
+        <v>114</v>
+      </c>
+      <c r="D105" s="2">
+        <v>109.97</v>
+      </c>
+      <c r="E105" s="2">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>45894</v>
+      </c>
+      <c r="B106" t="s">
+        <v>10</v>
+      </c>
+      <c r="C106" s="5">
+        <v>39</v>
+      </c>
+      <c r="D106" s="2">
+        <v>39.67</v>
+      </c>
+      <c r="E106" s="2">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107" s="1">
+        <v>45895</v>
+      </c>
+      <c r="B107" t="s">
+        <v>4</v>
+      </c>
+      <c r="C107" s="5">
+        <v>3110.78</v>
+      </c>
+      <c r="D107" s="2">
+        <v>1</v>
+      </c>
+      <c r="E107" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A108" s="1">
+        <v>45895</v>
+      </c>
+      <c r="B108" t="s">
+        <v>12</v>
+      </c>
+      <c r="C108" s="5">
+        <v>-17</v>
+      </c>
+      <c r="D108" s="2">
+        <v>117.12</v>
+      </c>
+      <c r="E108" s="2">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A109" s="1">
+        <v>45895</v>
+      </c>
+      <c r="B109" t="s">
+        <v>23</v>
+      </c>
+      <c r="C109" s="5">
+        <v>10</v>
+      </c>
+      <c r="D109" s="2">
+        <v>686.69</v>
+      </c>
+      <c r="E109" s="2">
+        <v>4.17</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
+        <v>45895</v>
+      </c>
+      <c r="B110" t="s">
+        <v>24</v>
+      </c>
+      <c r="C110" s="5">
+        <v>100</v>
+      </c>
+      <c r="D110" s="2">
+        <v>40.42</v>
+      </c>
+      <c r="E110" s="2">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A111" s="1">
+        <v>45901</v>
+      </c>
+      <c r="B111" t="s">
+        <v>12</v>
+      </c>
+      <c r="C111" s="5">
+        <v>-135</v>
+      </c>
+      <c r="D111" s="2">
+        <v>117.22</v>
+      </c>
+      <c r="E111" s="2">
+        <v>8.65</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A112" s="1">
+        <v>45902</v>
+      </c>
+      <c r="B112" t="s">
+        <v>25</v>
+      </c>
+      <c r="C112" s="5">
+        <v>3</v>
+      </c>
+      <c r="D112" s="2">
+        <v>192.47</v>
+      </c>
+      <c r="E112" s="2">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113" s="1">
+        <v>45902</v>
+      </c>
+      <c r="B113" t="s">
+        <v>10</v>
+      </c>
+      <c r="C113" s="5">
+        <v>-18</v>
+      </c>
+      <c r="D113" s="2">
+        <v>39.450000000000003</v>
+      </c>
+      <c r="E113" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114" s="1">
+        <v>45902</v>
+      </c>
+      <c r="B114" t="s">
+        <v>26</v>
+      </c>
+      <c r="C114" s="5">
+        <v>4</v>
+      </c>
+      <c r="D114" s="2">
+        <v>160.04</v>
+      </c>
+      <c r="E114" s="2">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A115" s="1">
+        <v>45902</v>
+      </c>
+      <c r="B115" t="s">
+        <v>24</v>
+      </c>
+      <c r="C115" s="5">
+        <v>-34</v>
+      </c>
+      <c r="D115" s="2">
+        <v>38.18</v>
+      </c>
+      <c r="E115" s="2">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A116" s="1">
+        <v>45902</v>
+      </c>
+      <c r="B116" t="s">
+        <v>14</v>
+      </c>
+      <c r="C116" s="5">
+        <v>-30</v>
+      </c>
+      <c r="D116" s="2">
+        <v>62.16</v>
+      </c>
+      <c r="E116" s="2">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A117" s="1">
+        <v>45902</v>
+      </c>
+      <c r="B117" t="s">
+        <v>27</v>
+      </c>
+      <c r="C117" s="5">
+        <v>8</v>
+      </c>
+      <c r="D117" s="2">
+        <v>70</v>
+      </c>
+      <c r="E117" s="2">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A118" s="1">
+        <v>45902</v>
+      </c>
+      <c r="B118" t="s">
+        <v>28</v>
+      </c>
+      <c r="C118" s="5">
+        <v>17</v>
+      </c>
+      <c r="D118" s="2">
+        <v>32.979999999999997</v>
+      </c>
+      <c r="E118" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A119" s="1">
+        <v>45915</v>
+      </c>
+      <c r="B119" t="s">
+        <v>23</v>
+      </c>
+      <c r="C119" s="5">
+        <v>13</v>
+      </c>
+      <c r="D119" s="2">
+        <v>706.4</v>
+      </c>
+      <c r="E119" s="2">
+        <v>5.01</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A120" s="1">
+        <v>45915</v>
+      </c>
+      <c r="B120" t="s">
+        <v>29</v>
+      </c>
+      <c r="C120" s="5">
+        <v>3</v>
+      </c>
+      <c r="D120" s="2">
+        <v>245</v>
+      </c>
+      <c r="E120" s="2">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A121" s="1">
+        <v>45915</v>
+      </c>
+      <c r="B121" t="s">
+        <v>10</v>
+      </c>
+      <c r="C121" s="5">
+        <v>-11</v>
+      </c>
+      <c r="D121" s="2">
+        <v>42.5</v>
+      </c>
+      <c r="E121" s="2">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A122" s="1">
+        <v>45915</v>
+      </c>
+      <c r="B122" t="s">
+        <v>24</v>
+      </c>
+      <c r="C122" s="5">
+        <v>-20</v>
+      </c>
+      <c r="D122" s="2">
+        <v>43.99</v>
+      </c>
+      <c r="E122" s="2">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A123" s="1">
+        <v>45915</v>
+      </c>
+      <c r="B123" t="s">
+        <v>6</v>
+      </c>
+      <c r="C123" s="5">
+        <v>7</v>
+      </c>
+      <c r="D123" s="2">
+        <v>336.31</v>
+      </c>
+      <c r="E123" s="2">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A124" s="1">
+        <v>45915</v>
+      </c>
+      <c r="B124" t="s">
+        <v>15</v>
+      </c>
+      <c r="C124" s="5">
+        <v>25</v>
+      </c>
+      <c r="D124" s="2">
+        <v>112.23</v>
+      </c>
+      <c r="E124" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A125" s="1">
+        <v>45915</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" s="5">
+        <v>12</v>
+      </c>
+      <c r="D125" s="2">
+        <v>52.58</v>
+      </c>
+      <c r="E125" s="2">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A126" s="1">
+        <v>45915</v>
+      </c>
+      <c r="B126" t="s">
+        <v>14</v>
+      </c>
+      <c r="C126" s="5">
+        <v>-17</v>
+      </c>
+      <c r="D126" s="2">
+        <v>65.33</v>
+      </c>
+      <c r="E126" s="2">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A127" s="1">
+        <v>45915</v>
+      </c>
+      <c r="B127" t="s">
+        <v>8</v>
+      </c>
+      <c r="C127" s="5">
+        <v>-8</v>
+      </c>
+      <c r="D127" s="2">
+        <v>90.15</v>
+      </c>
+      <c r="E127" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A128" s="1">
+        <v>45915</v>
+      </c>
+      <c r="B128" t="s">
+        <v>20</v>
+      </c>
+      <c r="C128" s="5">
+        <v>-6</v>
+      </c>
+      <c r="D128" s="2">
+        <v>108.18</v>
+      </c>
+      <c r="E128" s="2">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A129" s="1">
+        <v>45922</v>
+      </c>
+      <c r="B129" t="s">
+        <v>10</v>
+      </c>
+      <c r="C129" s="5">
+        <v>-8</v>
+      </c>
+      <c r="D129" s="2">
+        <v>49.22</v>
+      </c>
+      <c r="E129" s="2">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A130" s="1">
+        <v>45922</v>
+      </c>
+      <c r="B130" t="s">
+        <v>20</v>
+      </c>
+      <c r="C130" s="5">
+        <v>-7</v>
+      </c>
+      <c r="D130" s="2">
+        <v>110.1</v>
+      </c>
+      <c r="E130" s="2">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A131" s="1">
+        <v>45922</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" s="5">
+        <v>-32</v>
+      </c>
+      <c r="D131" s="2">
+        <v>53.06</v>
+      </c>
+      <c r="E131" s="2">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A132" s="1">
+        <v>45922</v>
+      </c>
+      <c r="B132" t="s">
+        <v>24</v>
+      </c>
+      <c r="C132" s="5">
+        <v>-12</v>
+      </c>
+      <c r="D132" s="2">
+        <v>45.94</v>
+      </c>
+      <c r="E132" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A133" s="1">
+        <v>45922</v>
+      </c>
+      <c r="B133" t="s">
+        <v>30</v>
+      </c>
+      <c r="C133" s="5">
+        <v>3</v>
+      </c>
+      <c r="D133" s="2">
+        <v>515.88</v>
+      </c>
+      <c r="E133" s="2">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A134" s="1">
+        <v>45923</v>
+      </c>
+      <c r="B134" t="s">
+        <v>6</v>
+      </c>
+      <c r="C134" s="5">
+        <v>5</v>
+      </c>
+      <c r="D134" s="2">
+        <v>347.91</v>
+      </c>
+      <c r="E134" s="2">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A135" s="1">
+        <v>45923</v>
+      </c>
+      <c r="B135" t="s">
+        <v>23</v>
+      </c>
+      <c r="C135" s="5">
+        <v>4</v>
+      </c>
+      <c r="D135" s="2">
+        <v>715.21</v>
+      </c>
+      <c r="E135" s="2">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A136" s="1">
+        <v>45929</v>
+      </c>
+      <c r="B136" t="s">
+        <v>31</v>
+      </c>
+      <c r="C136" s="5">
+        <v>8</v>
+      </c>
+      <c r="D136" s="2">
+        <v>128.72</v>
+      </c>
+      <c r="E136" s="2">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A137" s="1">
+        <v>45929</v>
+      </c>
+      <c r="B137" t="s">
+        <v>14</v>
+      </c>
+      <c r="C137" s="5">
+        <v>-25</v>
+      </c>
+      <c r="D137" s="2">
+        <v>64.37</v>
+      </c>
+      <c r="E137" s="2">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A138" s="1">
+        <v>45929</v>
+      </c>
+      <c r="B138" t="s">
+        <v>26</v>
+      </c>
+      <c r="C138" s="5">
+        <v>-4</v>
+      </c>
+      <c r="D138" s="2">
+        <v>183.17</v>
+      </c>
+      <c r="E138" s="2">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A139" s="1">
+        <v>45929</v>
+      </c>
+      <c r="B139" t="s">
+        <v>28</v>
+      </c>
+      <c r="C139" s="5">
+        <v>-17</v>
+      </c>
+      <c r="D139" s="2">
+        <v>38.380000000000003</v>
+      </c>
+      <c r="E139" s="2">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A140" s="1">
+        <v>45929</v>
+      </c>
+      <c r="B140" t="s">
+        <v>32</v>
+      </c>
+      <c r="C140" s="5">
+        <v>89</v>
+      </c>
+      <c r="D140" s="2">
+        <v>101.25</v>
+      </c>
+      <c r="E140" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A141" s="1">
+        <v>45929</v>
+      </c>
+      <c r="B141" t="s">
+        <v>8</v>
+      </c>
+      <c r="C141" s="5">
+        <v>-24</v>
+      </c>
+      <c r="D141" s="2">
+        <v>89.31</v>
+      </c>
+      <c r="E141" s="2">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A142" s="1">
+        <v>45929</v>
+      </c>
+      <c r="B142" t="s">
+        <v>24</v>
+      </c>
+      <c r="C142" s="5">
+        <v>-6</v>
+      </c>
+      <c r="D142" s="2">
+        <v>43.39</v>
+      </c>
+      <c r="E142" s="2">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A143" s="1">
+        <v>45929</v>
+      </c>
+      <c r="B143" t="s">
+        <v>15</v>
+      </c>
+      <c r="C143" s="5">
+        <v>-61</v>
+      </c>
+      <c r="D143" s="2">
+        <v>111.46</v>
+      </c>
+      <c r="E143" s="2">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A144" s="1">
+        <v>45929</v>
+      </c>
+      <c r="B144" t="s">
+        <v>5</v>
+      </c>
+      <c r="C144" s="5">
+        <v>13</v>
+      </c>
+      <c r="D144" s="2">
+        <v>664.34</v>
+      </c>
+      <c r="E144" s="2">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A145" s="1">
+        <v>45929</v>
+      </c>
+      <c r="B145" t="s">
+        <v>6</v>
+      </c>
+      <c r="C145" s="5">
+        <v>-5</v>
+      </c>
+      <c r="D145" s="2">
+        <v>351.8</v>
+      </c>
+      <c r="E145" s="2">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A146" s="1">
+        <v>45929</v>
+      </c>
+      <c r="B146" t="s">
+        <v>20</v>
+      </c>
+      <c r="C146" s="5">
+        <v>116</v>
+      </c>
+      <c r="D146" s="2">
+        <v>110.68</v>
+      </c>
+      <c r="E146" s="2">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A147" s="1">
+        <v>45929</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" s="5">
+        <v>-21</v>
+      </c>
+      <c r="D147" s="2">
+        <v>53.24</v>
+      </c>
+      <c r="E147" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A148" s="1">
+        <v>45929</v>
+      </c>
+      <c r="B148" t="s">
+        <v>14</v>
+      </c>
+      <c r="C148" s="5">
+        <v>-9</v>
+      </c>
+      <c r="D148" s="2">
+        <v>63.74</v>
+      </c>
+      <c r="E148" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A149" s="1">
+        <v>45929</v>
+      </c>
+      <c r="B149" t="s">
+        <v>23</v>
+      </c>
+      <c r="C149" s="5">
+        <v>-11</v>
+      </c>
+      <c r="D149" s="2">
+        <v>712.91</v>
+      </c>
+      <c r="E149" s="2">
+        <v>4.3600000000000003</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A150" s="1">
+        <v>45943</v>
+      </c>
+      <c r="B150" t="s">
+        <v>33</v>
+      </c>
+      <c r="C150" s="5">
+        <v>20</v>
+      </c>
+      <c r="D150" s="2">
+        <v>31.05</v>
+      </c>
+      <c r="E150" s="2">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A151" s="1">
+        <v>45943</v>
+      </c>
+      <c r="B151" t="s">
+        <v>32</v>
+      </c>
+      <c r="C151" s="5">
+        <v>-14</v>
+      </c>
+      <c r="D151" s="2">
+        <v>122.59</v>
+      </c>
+      <c r="E151" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A152" s="1">
+        <v>45943</v>
+      </c>
+      <c r="B152" t="s">
+        <v>8</v>
+      </c>
+      <c r="C152" s="5">
+        <v>16</v>
+      </c>
+      <c r="D152" s="2">
+        <v>90.28</v>
+      </c>
+      <c r="E152" s="2">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A153" s="1">
+        <v>45943</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" s="5">
+        <v>-28</v>
+      </c>
+      <c r="D153" s="2">
+        <v>53.44</v>
+      </c>
+      <c r="E153" s="2">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A154" s="1">
+        <v>45943</v>
+      </c>
+      <c r="B154" t="s">
+        <v>6</v>
+      </c>
+      <c r="C154" s="5">
+        <v>-8</v>
+      </c>
+      <c r="D154" s="2">
+        <v>376.5</v>
+      </c>
+      <c r="E154" s="2">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A155" s="1">
+        <v>45943</v>
+      </c>
+      <c r="B155" t="s">
+        <v>25</v>
+      </c>
+      <c r="C155" s="5">
+        <v>-3</v>
+      </c>
+      <c r="D155" s="2">
+        <v>414.76</v>
+      </c>
+      <c r="E155" s="2">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A156" s="1">
+        <v>45943</v>
+      </c>
+      <c r="B156" t="s">
+        <v>20</v>
+      </c>
+      <c r="C156" s="5">
+        <v>9</v>
+      </c>
+      <c r="D156" s="2">
+        <v>108.04</v>
+      </c>
+      <c r="E156" s="2">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A157" s="1">
+        <v>45943</v>
+      </c>
+      <c r="B157" t="s">
+        <v>15</v>
+      </c>
+      <c r="C157" s="5">
+        <v>20</v>
+      </c>
+      <c r="D157" s="2">
+        <v>111.4</v>
+      </c>
+      <c r="E157" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A158" s="1">
+        <v>45943</v>
+      </c>
+      <c r="B158" t="s">
+        <v>23</v>
+      </c>
+      <c r="C158" s="5">
+        <v>-6</v>
+      </c>
+      <c r="D158" s="2">
+        <v>710.59</v>
+      </c>
+      <c r="E158" s="2">
+        <v>2.41</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E24" xr:uid="{1EBC9900-0457-4E2A-A65B-407C2F1035D0}">
+  <autoFilter ref="A1:E97" xr:uid="{1EBC9900-0457-4E2A-A65B-407C2F1035D0}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E24">
       <sortCondition ref="A1:A24"/>
     </sortState>

--- a/portfolio_tracker.xlsx
+++ b/portfolio_tracker.xlsx
@@ -1,47 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexr\AlgoTester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B6964AD-1156-4475-B86F-F58A2740A256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF364B9-B739-4C6F-B6F9-5400657D7BD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$E$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Sheet2!$A$1:$E$170</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="34">
   <si>
     <t>date</t>
+  </si>
+  <si>
+    <t>ticker</t>
   </si>
   <si>
     <t>quantity</t>
@@ -72,9 +59,6 @@
   </si>
   <si>
     <t>URA</t>
-  </si>
-  <si>
-    <t>ticker</t>
   </si>
   <si>
     <t>IB01.L</t>
@@ -147,9 +131,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -163,7 +144,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -174,7 +154,14 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -183,24 +170,33 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -247,20 +243,20 @@
         <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -290,12 +286,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -334,667 +330,694 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:tint val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="9500"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:tint val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EBC9900-0457-4E2A-A65B-407C2F1035D0}">
-  <dimension ref="A1:H158"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:H181"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
         <v>45748</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="4">
+        <v>5</v>
+      </c>
+      <c r="C2" s="5">
         <v>63886</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="6">
         <v>1</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
         <v>45748</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="5">
         <v>9</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="6">
         <v>557.48</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="6">
         <v>1.01</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+    <row r="4" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
         <v>45748</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5">
         <v>65</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="6">
         <v>288.64</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="6">
         <v>0.79</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+    <row r="5" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
         <v>45748</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="5">
         <v>364</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="6">
         <v>110.1</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="6">
         <v>2.44</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>45753</v>
+    <row r="6" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>45754</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" s="5">
         <v>1500</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="6">
         <v>1</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
+    <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
         <v>45754</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" s="5">
         <v>35</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="6">
         <v>110.2</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="6">
         <v>0.45</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
+    <row r="8" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
         <v>45754</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" s="5">
         <v>-45</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="6">
         <v>278.69</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="6">
         <v>0.85</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
+    <row r="9" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
         <v>45754</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" s="5">
         <v>91</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="6">
         <v>91.85</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="6">
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
+    <row r="10" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
         <v>45761</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" s="5">
         <v>-7</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="6">
         <v>544</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="6">
         <v>0.51</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
+    <row r="11" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
         <v>45761</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" s="5">
         <v>-91</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="6">
         <v>87.42</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="6">
         <v>0.81</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
+    <row r="12" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
         <v>45761</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12" s="5">
         <v>76</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="6">
         <v>295.41000000000003</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="6">
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
+    <row r="13" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
         <v>45761</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13" s="5">
         <v>-86</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="6">
         <v>110.25</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="6">
         <v>0.85</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
+    <row r="14" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
         <v>45762</v>
       </c>
       <c r="B14" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" s="5">
         <v>1500</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="6">
         <v>1</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
+    <row r="15" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
         <v>45768</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" s="5">
         <v>3</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="6">
         <v>521.11</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="6">
         <v>0.39</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
+    <row r="16" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
         <v>45768</v>
       </c>
       <c r="B16" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C16" s="5">
         <v>59</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="6">
         <v>314.95999999999998</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="6">
         <v>0.49</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
+    <row r="17" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
         <v>45768</v>
       </c>
       <c r="B17" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C17" s="5">
         <v>-63</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="6">
         <v>110.35</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="6">
         <v>1.51</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
+    <row r="18" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
         <v>45768</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C18" s="5">
         <v>11</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="6">
         <v>88.45</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="6">
         <v>0.4</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
+    <row r="19" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4">
         <v>45768</v>
       </c>
       <c r="B19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19" s="5">
         <v>45</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="6">
         <v>22.95</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="6">
         <v>0.46</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
+    <row r="20" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4">
         <v>45768</v>
       </c>
       <c r="B20" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C20" s="5">
         <v>-100</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="6">
         <v>110.34</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="6">
         <v>1.5</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
+    <row r="21" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
         <v>45775</v>
       </c>
       <c r="B21" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C21" s="5">
         <v>-143</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="6">
         <v>110.43</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="6">
         <v>1.32</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
+    <row r="22" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4">
         <v>45775</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C22" s="5">
         <v>153</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="6">
         <v>88.66</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E22" s="6">
         <v>0.87</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
+    <row r="23" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4">
         <v>45775</v>
       </c>
       <c r="B23" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C23" s="5">
         <v>16</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="6">
         <v>551.34</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E23" s="6">
         <v>0.41</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
+    <row r="24" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4">
         <v>45775</v>
       </c>
       <c r="B24" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C24" s="5">
         <v>-23</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="6">
         <v>304.14999999999998</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24" s="6">
         <v>0.64</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
+    <row r="25" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4">
         <v>45782</v>
       </c>
       <c r="B25" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C25" s="5">
         <v>-106</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="6">
         <v>305.95</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25" s="6">
         <v>1.61</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
+    <row r="26" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="4">
         <v>45782</v>
       </c>
       <c r="B26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C26" s="5">
         <v>-153</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="6">
         <v>87.36</v>
       </c>
-      <c r="E26" s="2">
+      <c r="E26" s="6">
         <v>1.31</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
+    <row r="27" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="4">
         <v>45782</v>
       </c>
       <c r="B27" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" s="5">
         <v>-10</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="6">
         <v>562.48</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="6">
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
+    <row r="28" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="4">
         <v>45782</v>
       </c>
       <c r="B28" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C28" s="5">
         <v>475</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="6">
         <v>110.12</v>
       </c>
-      <c r="E28" s="2">
+      <c r="E28" s="6">
         <v>2.71</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
+    <row r="29" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="4">
         <v>45784</v>
       </c>
       <c r="B29" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C29" s="5">
         <v>1550</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="6">
         <v>1</v>
       </c>
-      <c r="E29" s="2">
+      <c r="E29" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
+    <row r="30" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="4">
         <v>45804</v>
       </c>
       <c r="B30" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C30" s="5">
         <v>-13</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="6">
         <v>32.799999999999997</v>
       </c>
-      <c r="E30" s="2">
+      <c r="E30" s="6">
         <v>0.41</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
+    <row r="31" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="4">
         <v>45804</v>
       </c>
       <c r="B31" t="s">
@@ -1003,83 +1026,83 @@
       <c r="C31" s="5">
         <v>427</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="6">
         <v>115.93</v>
       </c>
-      <c r="E31" s="2">
+      <c r="E31" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
+    <row r="32" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="4">
         <v>45804</v>
       </c>
       <c r="B32" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C32" s="5">
         <v>2</v>
       </c>
-      <c r="D32" s="2">
+      <c r="D32" s="6">
         <v>303.83999999999997</v>
       </c>
-      <c r="E32" s="2">
+      <c r="E32" s="6">
         <v>0.39</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="1">
+    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="4">
         <v>45804</v>
       </c>
       <c r="B33" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C33" s="5">
         <v>9</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33" s="6">
         <v>586.14</v>
       </c>
-      <c r="E33" s="2">
+      <c r="E33" s="6">
         <v>0.4</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
+    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="4">
         <v>45804</v>
       </c>
       <c r="B34" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C34" s="5">
         <v>-482</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="6">
         <v>110.39</v>
       </c>
-      <c r="E34" s="2">
+      <c r="E34" s="6">
         <v>2.84</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="1">
+    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="4">
         <v>45824</v>
       </c>
       <c r="B35" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C35" s="5">
         <v>4689</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="6">
         <v>1</v>
       </c>
-      <c r="E35" s="2">
+      <c r="E35" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="1">
+    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="4">
         <v>45824</v>
       </c>
       <c r="B36" t="s">
@@ -1088,15 +1111,15 @@
       <c r="C36" s="5">
         <v>1</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36" s="6">
         <v>79.05</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E36" s="6">
         <v>0.38</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="1">
+    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="4">
         <v>45824</v>
       </c>
       <c r="B37" t="s">
@@ -1105,15 +1128,15 @@
       <c r="C37" s="5">
         <v>25</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="6">
         <v>60.61</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="6">
         <v>0.43</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="1">
+    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="4">
         <v>45824</v>
       </c>
       <c r="B38" t="s">
@@ -1122,15 +1145,15 @@
       <c r="C38" s="5">
         <v>486</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38" s="6">
         <v>107.8</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E38" s="6">
         <v>2.25</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="1">
+    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="4">
         <v>45824</v>
       </c>
       <c r="B39" t="s">
@@ -1139,15 +1162,15 @@
       <c r="C39" s="5">
         <v>1</v>
       </c>
-      <c r="D39" s="2">
+      <c r="D39" s="6">
         <v>47.2</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E39" s="6">
         <v>0.38</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="1">
+    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="4">
         <v>45824</v>
       </c>
       <c r="B40" t="s">
@@ -1156,33 +1179,33 @@
       <c r="C40" s="5">
         <v>500</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D40" s="6">
         <v>26.98</v>
       </c>
-      <c r="E40" s="2">
+      <c r="E40" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="1">
+    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="4">
         <v>45824</v>
       </c>
       <c r="B41" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C41" s="5">
         <v>9</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D41" s="6">
         <v>314.77</v>
       </c>
-      <c r="E41" s="2">
+      <c r="E41" s="6">
         <v>0.39</v>
       </c>
-      <c r="H41" s="2"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="1">
+      <c r="H41" s="6"/>
+    </row>
+    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="4">
         <v>45824</v>
       </c>
       <c r="B42" t="s">
@@ -1191,32 +1214,32 @@
       <c r="C42" s="5">
         <v>-427</v>
       </c>
-      <c r="D42" s="2">
+      <c r="D42" s="6">
         <v>116.14</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E42" s="6">
         <v>19</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="1">
+    <row r="43" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="4">
         <v>45824</v>
       </c>
       <c r="B43" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C43" s="5">
         <v>-14</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="6">
         <v>600.34</v>
       </c>
-      <c r="E43" s="2">
+      <c r="E43" s="6">
         <v>0.4</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="1">
+    <row r="44" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="4">
         <v>45831</v>
       </c>
       <c r="B44" t="s">
@@ -1225,15 +1248,15 @@
       <c r="C44" s="5">
         <v>90</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="6">
         <v>116.24</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E44" s="6">
         <v>5.72</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="1">
+    <row r="45" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="4">
         <v>45831</v>
       </c>
       <c r="B45" t="s">
@@ -1242,15 +1265,15 @@
       <c r="C45" s="5">
         <v>-61</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="6">
         <v>46.25</v>
       </c>
-      <c r="E45" s="2">
+      <c r="E45" s="6">
         <v>0.44</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="1">
+    <row r="46" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="4">
         <v>45831</v>
       </c>
       <c r="B46" t="s">
@@ -1259,15 +1282,15 @@
       <c r="C46" s="5">
         <v>202</v>
       </c>
-      <c r="D46" s="2">
+      <c r="D46" s="6">
         <v>57.47</v>
       </c>
-      <c r="E46" s="2">
+      <c r="E46" s="6">
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="1">
+    <row r="47" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="4">
         <v>45831</v>
       </c>
       <c r="B47" t="s">
@@ -1276,15 +1299,15 @@
       <c r="C47" s="5">
         <v>-263</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="6">
         <v>108.39</v>
       </c>
-      <c r="E47" s="2">
+      <c r="E47" s="6">
         <v>1.26</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="1">
+    <row r="48" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="4">
         <v>45838</v>
       </c>
       <c r="B48" t="s">
@@ -1293,15 +1316,15 @@
       <c r="C48" s="5">
         <v>-305</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D48" s="6">
         <v>61.27</v>
       </c>
-      <c r="E48" s="2">
+      <c r="E48" s="6">
         <v>1.65</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="1">
+    <row r="49" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="4">
         <v>45838</v>
       </c>
       <c r="B49" t="s">
@@ -1310,15 +1333,15 @@
       <c r="C49" s="5">
         <v>432</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="6">
         <v>26.25</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E49" s="6">
         <v>1.83</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="1">
+    <row r="50" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="4">
         <v>45838</v>
       </c>
       <c r="B50" t="s">
@@ -1327,32 +1350,32 @@
       <c r="C50" s="5">
         <v>-54</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D50" s="6">
         <v>48.02</v>
       </c>
-      <c r="E50" s="2">
+      <c r="E50" s="6">
         <v>0.41</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="1">
+    <row r="51" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="4">
         <v>45838</v>
       </c>
       <c r="B51" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C51" s="5">
         <v>-14</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D51" s="6">
         <v>302.33</v>
       </c>
-      <c r="E51" s="2">
+      <c r="E51" s="6">
         <v>0.36</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="1">
+    <row r="52" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="4">
         <v>45838</v>
       </c>
       <c r="B52" t="s">
@@ -1361,66 +1384,66 @@
       <c r="C52" s="5">
         <v>190</v>
       </c>
-      <c r="D52" s="2">
+      <c r="D52" s="6">
         <v>109.3</v>
       </c>
-      <c r="E52" s="2">
+      <c r="E52" s="6">
         <v>0.81</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="1">
+    <row r="53" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="4">
         <v>45838</v>
       </c>
       <c r="B53" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C53" s="5">
         <v>-47</v>
       </c>
-      <c r="D53" s="2">
+      <c r="D53" s="6">
         <v>122.61</v>
       </c>
-      <c r="E53" s="2">
+      <c r="E53" s="6">
         <v>0.39</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="1">
+    <row r="54" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="4">
         <v>45838</v>
       </c>
       <c r="B54" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C54" s="5">
         <v>14</v>
       </c>
-      <c r="D54" s="2">
+      <c r="D54" s="6">
         <v>617.42999999999995</v>
       </c>
-      <c r="E54" s="2">
+      <c r="E54" s="6">
         <v>0.36</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" s="1">
+    <row r="55" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="4">
         <v>45838</v>
       </c>
       <c r="B55" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C55" s="5">
         <v>-71</v>
       </c>
-      <c r="D55" s="2">
+      <c r="D55" s="6">
         <v>38.75</v>
       </c>
-      <c r="E55" s="2">
+      <c r="E55" s="6">
         <v>0.41</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="1">
+    <row r="56" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="4">
         <v>45838</v>
       </c>
       <c r="B56" t="s">
@@ -1429,32 +1452,32 @@
       <c r="C56" s="5">
         <v>110</v>
       </c>
-      <c r="D56" s="2">
+      <c r="D56" s="6">
         <v>73.48</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="6">
         <v>0.47</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="1">
+    <row r="57" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="4">
         <v>45852</v>
       </c>
       <c r="B57" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C57" s="5">
         <v>2336</v>
       </c>
-      <c r="D57" s="2">
+      <c r="D57" s="6">
         <v>1</v>
       </c>
-      <c r="E57" s="2">
+      <c r="E57" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" s="1">
+    <row r="58" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="4">
         <v>45852</v>
       </c>
       <c r="B58" t="s">
@@ -1463,32 +1486,32 @@
       <c r="C58" s="5">
         <v>82</v>
       </c>
-      <c r="D58" s="2">
+      <c r="D58" s="6">
         <v>69.2</v>
       </c>
-      <c r="E58" s="2">
+      <c r="E58" s="6">
         <v>0.54</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" s="1">
+    <row r="59" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="4">
         <v>45852</v>
       </c>
       <c r="B59" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C59" s="5">
         <v>60</v>
       </c>
-      <c r="D59" s="2">
+      <c r="D59" s="6">
         <v>309.12</v>
       </c>
-      <c r="E59" s="2">
+      <c r="E59" s="6">
         <v>0.43</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" s="1">
+    <row r="60" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="4">
         <v>45852</v>
       </c>
       <c r="B60" t="s">
@@ -1497,32 +1520,32 @@
       <c r="C60" s="5">
         <v>495</v>
       </c>
-      <c r="D60" s="2">
+      <c r="D60" s="6">
         <v>48.27</v>
       </c>
-      <c r="E60" s="2">
+      <c r="E60" s="6">
         <v>2.2799999999999998</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="1">
+    <row r="61" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="4">
         <v>45852</v>
       </c>
       <c r="B61" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C61" s="5">
         <v>-18</v>
       </c>
-      <c r="D61" s="2">
+      <c r="D61" s="6">
         <v>623.20000000000005</v>
       </c>
-      <c r="E61" s="2">
+      <c r="E61" s="6">
         <v>0.4</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" s="1">
+    <row r="62" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="4">
         <v>45852</v>
       </c>
       <c r="B62" t="s">
@@ -1531,15 +1554,15 @@
       <c r="C62" s="5">
         <v>-111</v>
       </c>
-      <c r="D62" s="2">
+      <c r="D62" s="6">
         <v>77.27</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62" s="6">
         <v>0.53</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" s="1">
+    <row r="63" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="4">
         <v>45852</v>
       </c>
       <c r="B63" t="s">
@@ -1548,32 +1571,32 @@
       <c r="C63" s="5">
         <v>34</v>
       </c>
-      <c r="D63" s="2">
+      <c r="D63" s="6">
         <v>34.04</v>
       </c>
-      <c r="E63" s="2">
+      <c r="E63" s="6">
         <v>0.41</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" s="1">
+    <row r="64" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="4">
         <v>45852</v>
       </c>
       <c r="B64" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C64" s="5">
         <v>70</v>
       </c>
-      <c r="D64" s="2">
+      <c r="D64" s="6">
         <v>37.6</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E64" s="6">
         <v>0.44</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65" s="1">
+    <row r="65" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="4">
         <v>45852</v>
       </c>
       <c r="B65" t="s">
@@ -1582,32 +1605,32 @@
       <c r="C65" s="5">
         <v>-932</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D65" s="6">
         <v>25.95</v>
       </c>
-      <c r="E65" s="2">
+      <c r="E65" s="6">
         <v>4.46</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" s="1">
+    <row r="66" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="4">
         <v>45852</v>
       </c>
       <c r="B66" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C66" s="5">
         <v>45</v>
       </c>
-      <c r="D66" s="2">
+      <c r="D66" s="6">
         <v>125</v>
       </c>
-      <c r="E66" s="2">
+      <c r="E66" s="6">
         <v>0.42</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="1">
+    <row r="67" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="4">
         <v>45852</v>
       </c>
       <c r="B67" t="s">
@@ -1616,15 +1639,15 @@
       <c r="C67" s="5">
         <v>-90</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D67" s="6">
         <v>108.02</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E67" s="6">
         <v>0.47</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="1">
+    <row r="68" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="4">
         <v>45859</v>
       </c>
       <c r="B68" t="s">
@@ -1633,32 +1656,32 @@
       <c r="C68" s="5">
         <v>-50</v>
       </c>
-      <c r="D68" s="2">
+      <c r="D68" s="6">
         <v>116.6</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E68" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" s="1">
+    <row r="69" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="4">
         <v>45859</v>
       </c>
       <c r="B69" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C69" s="5">
         <v>6</v>
       </c>
-      <c r="D69" s="2">
+      <c r="D69" s="6">
         <v>41.6</v>
       </c>
-      <c r="E69" s="2">
+      <c r="E69" s="6">
         <v>0.39</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70" s="1">
+    <row r="70" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="4">
         <v>45859</v>
       </c>
       <c r="B70" t="s">
@@ -1667,15 +1690,15 @@
       <c r="C70" s="5">
         <v>164</v>
       </c>
-      <c r="D70" s="2">
+      <c r="D70" s="6">
         <v>9.4499999999999993</v>
       </c>
-      <c r="E70" s="2">
+      <c r="E70" s="6">
         <v>0.76</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" s="1">
+    <row r="71" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="4">
         <v>45859</v>
       </c>
       <c r="B71" t="s">
@@ -1684,15 +1707,15 @@
       <c r="C71" s="5">
         <v>-142</v>
       </c>
-      <c r="D71" s="2">
+      <c r="D71" s="6">
         <v>49.33</v>
       </c>
-      <c r="E71" s="2">
+      <c r="E71" s="6">
         <v>0.68</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72" s="1">
+    <row r="72" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="4">
         <v>45859</v>
       </c>
       <c r="B72" t="s">
@@ -1701,49 +1724,49 @@
       <c r="C72" s="5">
         <v>-159</v>
       </c>
-      <c r="D72" s="2">
+      <c r="D72" s="6">
         <v>108.86</v>
       </c>
-      <c r="E72" s="2">
+      <c r="E72" s="6">
         <v>0.76</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" s="1">
+    <row r="73" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="4">
         <v>45859</v>
       </c>
       <c r="B73" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C73" s="5">
         <v>2</v>
       </c>
-      <c r="D73" s="2">
+      <c r="D73" s="6">
         <v>132.76</v>
       </c>
-      <c r="E73" s="2">
+      <c r="E73" s="6">
         <v>0.38</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74" s="1">
+    <row r="74" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="4">
         <v>45859</v>
       </c>
       <c r="B74" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C74" s="5">
         <v>-18</v>
       </c>
-      <c r="D74" s="2">
+      <c r="D74" s="6">
         <v>311.88</v>
       </c>
-      <c r="E74" s="2">
+      <c r="E74" s="6">
         <v>0.4</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" s="1">
+    <row r="75" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="4">
         <v>45859</v>
       </c>
       <c r="B75" t="s">
@@ -1752,32 +1775,32 @@
       <c r="C75" s="5">
         <v>108</v>
       </c>
-      <c r="D75" s="2">
+      <c r="D75" s="6">
         <v>95.67</v>
       </c>
-      <c r="E75" s="2">
+      <c r="E75" s="6">
         <v>0.5</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76" s="1">
+    <row r="76" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="4">
         <v>45859</v>
       </c>
       <c r="B76" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C76" s="5">
         <v>7</v>
       </c>
-      <c r="D76" s="2">
+      <c r="D76" s="6">
         <v>628.74</v>
       </c>
-      <c r="E76" s="2">
+      <c r="E76" s="6">
         <v>0.39</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77" s="1">
+    <row r="77" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="4">
         <v>45859</v>
       </c>
       <c r="B77" t="s">
@@ -1786,15 +1809,15 @@
       <c r="C77" s="5">
         <v>643</v>
       </c>
-      <c r="D77" s="2">
+      <c r="D77" s="6">
         <v>2.74</v>
       </c>
-      <c r="E77" s="2">
+      <c r="E77" s="6">
         <v>3.66</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78" s="1">
+    <row r="78" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="4">
         <v>45866</v>
       </c>
       <c r="B78" t="s">
@@ -1803,32 +1826,32 @@
       <c r="C78" s="5">
         <v>-321</v>
       </c>
-      <c r="D78" s="2">
+      <c r="D78" s="6">
         <v>3</v>
       </c>
-      <c r="E78" s="2">
+      <c r="E78" s="6">
         <v>1.89</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79" s="1">
+    <row r="79" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="4">
         <v>45866</v>
       </c>
       <c r="B79" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C79" s="5">
         <v>4</v>
       </c>
-      <c r="D79" s="2">
+      <c r="D79" s="6">
         <v>637.49</v>
       </c>
-      <c r="E79" s="2">
+      <c r="E79" s="6">
         <v>0.38</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" s="1">
+    <row r="80" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="4">
         <v>45866</v>
       </c>
       <c r="B80" t="s">
@@ -1837,32 +1860,32 @@
       <c r="C80" s="5">
         <v>95</v>
       </c>
-      <c r="D80" s="2">
+      <c r="D80" s="6">
         <v>67.400000000000006</v>
       </c>
-      <c r="E80" s="2">
+      <c r="E80" s="6">
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" s="1">
+    <row r="81" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="4">
         <v>45866</v>
       </c>
       <c r="B81" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C81" s="5">
         <v>52</v>
       </c>
-      <c r="D81" s="2">
+      <c r="D81" s="6">
         <v>86</v>
       </c>
-      <c r="E81" s="2">
+      <c r="E81" s="6">
         <v>0.48</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A82" s="1">
+    <row r="82" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="4">
         <v>45866</v>
       </c>
       <c r="B82" t="s">
@@ -1871,15 +1894,15 @@
       <c r="C82" s="5">
         <v>-131</v>
       </c>
-      <c r="D82" s="2">
+      <c r="D82" s="6">
         <v>108.86</v>
       </c>
-      <c r="E82" s="2">
+      <c r="E82" s="6">
         <v>0.63</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A83" s="1">
+    <row r="83" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="4">
         <v>45866</v>
       </c>
       <c r="B83" t="s">
@@ -1888,15 +1911,15 @@
       <c r="C83" s="5">
         <v>211</v>
       </c>
-      <c r="D83" s="2">
+      <c r="D83" s="6">
         <v>49.31</v>
       </c>
-      <c r="E83" s="2">
+      <c r="E83" s="6">
         <v>0.44</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A84" s="1">
+    <row r="84" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="4">
         <v>45866</v>
       </c>
       <c r="B84" t="s">
@@ -1905,15 +1928,15 @@
       <c r="C84" s="5">
         <v>-64</v>
       </c>
-      <c r="D84" s="2">
+      <c r="D84" s="6">
         <v>10.3</v>
       </c>
-      <c r="E84" s="2">
+      <c r="E84" s="6">
         <v>0.44</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85" s="1">
+    <row r="85" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="4">
         <v>45866</v>
       </c>
       <c r="B85" t="s">
@@ -1922,66 +1945,66 @@
       <c r="C85" s="5">
         <v>64</v>
       </c>
-      <c r="D85" s="2">
+      <c r="D85" s="6">
         <v>36.28</v>
       </c>
-      <c r="E85" s="2">
+      <c r="E85" s="6">
         <v>0.43</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A86" s="1">
+    <row r="86" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="4">
         <v>45866</v>
       </c>
       <c r="B86" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C86" s="5">
         <v>-53</v>
       </c>
-      <c r="D86" s="2">
+      <c r="D86" s="6">
         <v>306.44</v>
       </c>
-      <c r="E86" s="2">
+      <c r="E86" s="6">
         <v>0.43</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A87" s="1">
+    <row r="87" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="4">
         <v>45866</v>
       </c>
       <c r="B87" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C87" s="5">
         <v>-10</v>
       </c>
-      <c r="D87" s="2">
+      <c r="D87" s="6">
         <v>41.57</v>
       </c>
-      <c r="E87" s="2">
+      <c r="E87" s="6">
         <v>0.39</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A88" s="1">
+    <row r="88" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="4">
         <v>45866</v>
       </c>
       <c r="B88" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C88" s="5">
         <v>-3</v>
       </c>
-      <c r="D88" s="2">
+      <c r="D88" s="6">
         <v>127.87</v>
       </c>
-      <c r="E88" s="2">
+      <c r="E88" s="6">
         <v>0.38</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A89" s="1">
+    <row r="89" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="4">
         <v>45866</v>
       </c>
       <c r="B89" t="s">
@@ -1990,15 +2013,15 @@
       <c r="C89" s="5">
         <v>-18</v>
       </c>
-      <c r="D89" s="2">
+      <c r="D89" s="6">
         <v>99.51</v>
       </c>
-      <c r="E89" s="2">
+      <c r="E89" s="6">
         <v>0.4</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A90" s="1">
+    <row r="90" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="4">
         <v>45866</v>
       </c>
       <c r="B90" t="s">
@@ -2007,15 +2030,15 @@
       <c r="C90" s="5">
         <v>112</v>
       </c>
-      <c r="D90" s="2">
+      <c r="D90" s="6">
         <v>116.7</v>
       </c>
-      <c r="E90" s="2">
+      <c r="E90" s="6">
         <v>7.85</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A91" s="1">
+    <row r="91" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="4">
         <v>45873</v>
       </c>
       <c r="B91" t="s">
@@ -2024,32 +2047,32 @@
       <c r="C91" s="5">
         <v>-322</v>
       </c>
-      <c r="D91" s="2">
+      <c r="D91" s="6">
         <v>2.37</v>
       </c>
-      <c r="E91" s="2">
+      <c r="E91" s="6">
         <v>1.74</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A92" s="1">
+    <row r="92" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="4">
         <v>45873</v>
       </c>
       <c r="B92" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C92" s="5">
         <v>52</v>
       </c>
-      <c r="D92" s="2">
+      <c r="D92" s="6">
         <v>87.95</v>
       </c>
-      <c r="E92" s="2">
+      <c r="E92" s="6">
         <v>0.44</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93" s="1">
+    <row r="93" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="4">
         <v>45873</v>
       </c>
       <c r="B93" t="s">
@@ -2058,15 +2081,15 @@
       <c r="C93" s="5">
         <v>-34</v>
       </c>
-      <c r="D93" s="2">
+      <c r="D93" s="6">
         <v>27.67</v>
       </c>
-      <c r="E93" s="2">
+      <c r="E93" s="6">
         <v>0.38</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A94" s="1">
+    <row r="94" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="4">
         <v>45873</v>
       </c>
       <c r="B94" t="s">
@@ -2075,15 +2098,15 @@
       <c r="C94" s="5">
         <v>-230</v>
       </c>
-      <c r="D94" s="2">
+      <c r="D94" s="6">
         <v>48.74</v>
       </c>
-      <c r="E94" s="2">
+      <c r="E94" s="6">
         <v>0.97</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" s="1">
+    <row r="95" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="4">
         <v>45873</v>
       </c>
       <c r="B95" t="s">
@@ -2092,32 +2115,32 @@
       <c r="C95" s="5">
         <v>50</v>
       </c>
-      <c r="D95" s="2">
+      <c r="D95" s="6">
         <v>109.78</v>
       </c>
-      <c r="E95" s="2">
+      <c r="E95" s="6">
         <v>0.39</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A96" s="1">
+    <row r="96" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="4">
         <v>45873</v>
       </c>
       <c r="B96" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C96" s="5">
         <v>-8</v>
       </c>
-      <c r="D96" s="2">
+      <c r="D96" s="6">
         <v>121.04</v>
       </c>
-      <c r="E96" s="2">
+      <c r="E96" s="6">
         <v>0.36</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" s="1">
+    <row r="97" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="4">
         <v>45873</v>
       </c>
       <c r="B97" t="s">
@@ -2126,32 +2149,32 @@
       <c r="C97" s="5">
         <v>-100</v>
       </c>
-      <c r="D97" s="2">
+      <c r="D97" s="6">
         <v>8.89</v>
       </c>
-      <c r="E97" s="2">
+      <c r="E97" s="6">
         <v>0.44</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="1">
+    <row r="98" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="4">
         <v>45894</v>
       </c>
       <c r="B98" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C98" s="5">
         <v>4</v>
       </c>
-      <c r="D98" s="2">
+      <c r="D98" s="6">
         <v>86.73</v>
       </c>
-      <c r="E98" s="2">
+      <c r="E98" s="6">
         <v>0.39</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="1">
+    <row r="99" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="4">
         <v>45894</v>
       </c>
       <c r="B99" t="s">
@@ -2160,32 +2183,32 @@
       <c r="C99" s="5">
         <v>-18</v>
       </c>
-      <c r="D99" s="2">
+      <c r="D99" s="6">
         <v>63.46</v>
       </c>
-      <c r="E99" s="2">
+      <c r="E99" s="6">
         <v>0.42</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A100" s="1">
+    <row r="100" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="4">
         <v>45894</v>
       </c>
       <c r="B100" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C100" s="5">
         <v>-13</v>
       </c>
-      <c r="D100" s="2">
+      <c r="D100" s="6">
         <v>644</v>
       </c>
-      <c r="E100" s="2">
+      <c r="E100" s="6">
         <v>0.39</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A101" s="1">
+    <row r="101" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="4">
         <v>45894</v>
       </c>
       <c r="B101" t="s">
@@ -2194,32 +2217,32 @@
       <c r="C101" s="5">
         <v>-35</v>
       </c>
-      <c r="D101" s="2">
+      <c r="D101" s="6">
         <v>101.39</v>
       </c>
-      <c r="E101" s="2">
+      <c r="E101" s="6">
         <v>0.42</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A102" s="1">
+    <row r="102" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="4">
         <v>45894</v>
       </c>
       <c r="B102" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C102" s="5">
         <v>7</v>
       </c>
-      <c r="D102" s="2">
+      <c r="D102" s="6">
         <v>309.67</v>
       </c>
-      <c r="E102" s="2">
+      <c r="E102" s="6">
         <v>0.39</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A103" s="1">
+    <row r="103" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="4">
         <v>45894</v>
       </c>
       <c r="B103" t="s">
@@ -2228,15 +2251,15 @@
       <c r="C103" s="5">
         <v>-64</v>
       </c>
-      <c r="D103" s="2">
+      <c r="D103" s="6">
         <v>37.25</v>
       </c>
-      <c r="E103" s="2">
+      <c r="E103" s="6">
         <v>0.44</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A104" s="1">
+    <row r="104" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="4">
         <v>45894</v>
       </c>
       <c r="B104" t="s">
@@ -2245,15 +2268,15 @@
       <c r="C104" s="5">
         <v>-62</v>
       </c>
-      <c r="D104" s="2">
+      <c r="D104" s="6">
         <v>50.53</v>
       </c>
-      <c r="E104" s="2">
+      <c r="E104" s="6">
         <v>0.44</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A105" s="1">
+    <row r="105" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="4">
         <v>45894</v>
       </c>
       <c r="B105" t="s">
@@ -2262,49 +2285,49 @@
       <c r="C105" s="5">
         <v>114</v>
       </c>
-      <c r="D105" s="2">
+      <c r="D105" s="6">
         <v>109.97</v>
       </c>
-      <c r="E105" s="2">
+      <c r="E105" s="6">
         <v>0.52</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A106" s="1">
+    <row r="106" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="4">
         <v>45894</v>
       </c>
       <c r="B106" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C106" s="5">
         <v>39</v>
       </c>
-      <c r="D106" s="2">
+      <c r="D106" s="6">
         <v>39.67</v>
       </c>
-      <c r="E106" s="2">
+      <c r="E106" s="6">
         <v>0.41</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A107" s="1">
+    <row r="107" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="4">
         <v>45895</v>
       </c>
       <c r="B107" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C107" s="5">
         <v>3110.78</v>
       </c>
-      <c r="D107" s="2">
+      <c r="D107" s="6">
         <v>1</v>
       </c>
-      <c r="E107" s="2">
+      <c r="E107" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A108" s="1">
+    <row r="108" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="4">
         <v>45895</v>
       </c>
       <c r="B108" t="s">
@@ -2313,15 +2336,15 @@
       <c r="C108" s="5">
         <v>-17</v>
       </c>
-      <c r="D108" s="2">
+      <c r="D108" s="6">
         <v>117.12</v>
       </c>
-      <c r="E108" s="2">
+      <c r="E108" s="6">
         <v>1.86</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109" s="1">
+    <row r="109" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="4">
         <v>45895</v>
       </c>
       <c r="B109" t="s">
@@ -2330,15 +2353,15 @@
       <c r="C109" s="5">
         <v>10</v>
       </c>
-      <c r="D109" s="2">
+      <c r="D109" s="6">
         <v>686.69</v>
       </c>
-      <c r="E109" s="2">
+      <c r="E109" s="6">
         <v>4.17</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A110" s="1">
+    <row r="110" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="4">
         <v>45895</v>
       </c>
       <c r="B110" t="s">
@@ -2347,15 +2370,15 @@
       <c r="C110" s="5">
         <v>100</v>
       </c>
-      <c r="D110" s="2">
+      <c r="D110" s="6">
         <v>40.42</v>
       </c>
-      <c r="E110" s="2">
+      <c r="E110" s="6">
         <v>0.73</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A111" s="1">
+    <row r="111" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="4">
         <v>45901</v>
       </c>
       <c r="B111" t="s">
@@ -2364,15 +2387,15 @@
       <c r="C111" s="5">
         <v>-135</v>
       </c>
-      <c r="D111" s="2">
+      <c r="D111" s="6">
         <v>117.22</v>
       </c>
-      <c r="E111" s="2">
+      <c r="E111" s="6">
         <v>8.65</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A112" s="1">
+    <row r="112" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="4">
         <v>45902</v>
       </c>
       <c r="B112" t="s">
@@ -2381,32 +2404,32 @@
       <c r="C112" s="5">
         <v>3</v>
       </c>
-      <c r="D112" s="2">
+      <c r="D112" s="6">
         <v>192.47</v>
       </c>
-      <c r="E112" s="2">
+      <c r="E112" s="6">
         <v>0.38</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A113" s="1">
+    <row r="113" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="4">
         <v>45902</v>
       </c>
       <c r="B113" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C113" s="5">
         <v>-18</v>
       </c>
-      <c r="D113" s="2">
+      <c r="D113" s="6">
         <v>39.450000000000003</v>
       </c>
-      <c r="E113" s="2">
+      <c r="E113" s="6">
         <v>0.4</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A114" s="1">
+    <row r="114" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="4">
         <v>45902</v>
       </c>
       <c r="B114" t="s">
@@ -2415,15 +2438,15 @@
       <c r="C114" s="5">
         <v>4</v>
       </c>
-      <c r="D114" s="2">
+      <c r="D114" s="6">
         <v>160.04</v>
       </c>
-      <c r="E114" s="2">
+      <c r="E114" s="6">
         <v>0.39</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A115" s="1">
+    <row r="115" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="4">
         <v>45902</v>
       </c>
       <c r="B115" t="s">
@@ -2432,15 +2455,15 @@
       <c r="C115" s="5">
         <v>-34</v>
       </c>
-      <c r="D115" s="2">
+      <c r="D115" s="6">
         <v>38.18</v>
       </c>
-      <c r="E115" s="2">
+      <c r="E115" s="6">
         <v>0.43</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A116" s="1">
+    <row r="116" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="4">
         <v>45902</v>
       </c>
       <c r="B116" t="s">
@@ -2449,15 +2472,15 @@
       <c r="C116" s="5">
         <v>-30</v>
       </c>
-      <c r="D116" s="2">
+      <c r="D116" s="6">
         <v>62.16</v>
       </c>
-      <c r="E116" s="2">
+      <c r="E116" s="6">
         <v>0.44</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A117" s="1">
+    <row r="117" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="4">
         <v>45902</v>
       </c>
       <c r="B117" t="s">
@@ -2466,15 +2489,15 @@
       <c r="C117" s="5">
         <v>8</v>
       </c>
-      <c r="D117" s="2">
+      <c r="D117" s="6">
         <v>70</v>
       </c>
-      <c r="E117" s="2">
+      <c r="E117" s="6">
         <v>0.39</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A118" s="1">
+    <row r="118" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="4">
         <v>45902</v>
       </c>
       <c r="B118" t="s">
@@ -2483,15 +2506,15 @@
       <c r="C118" s="5">
         <v>17</v>
       </c>
-      <c r="D118" s="2">
+      <c r="D118" s="6">
         <v>32.979999999999997</v>
       </c>
-      <c r="E118" s="2">
+      <c r="E118" s="6">
         <v>0.4</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A119" s="1">
+    <row r="119" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="4">
         <v>45915</v>
       </c>
       <c r="B119" t="s">
@@ -2500,15 +2523,15 @@
       <c r="C119" s="5">
         <v>13</v>
       </c>
-      <c r="D119" s="2">
+      <c r="D119" s="6">
         <v>706.4</v>
       </c>
-      <c r="E119" s="2">
+      <c r="E119" s="6">
         <v>5.01</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A120" s="1">
+    <row r="120" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="4">
         <v>45915</v>
       </c>
       <c r="B120" t="s">
@@ -2517,32 +2540,32 @@
       <c r="C120" s="5">
         <v>3</v>
       </c>
-      <c r="D120" s="2">
+      <c r="D120" s="6">
         <v>245</v>
       </c>
-      <c r="E120" s="2">
+      <c r="E120" s="6">
         <v>0.39</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A121" s="1">
+    <row r="121" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="4">
         <v>45915</v>
       </c>
       <c r="B121" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C121" s="5">
         <v>-11</v>
       </c>
-      <c r="D121" s="2">
+      <c r="D121" s="6">
         <v>42.5</v>
       </c>
-      <c r="E121" s="2">
+      <c r="E121" s="6">
         <v>0.39</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A122" s="1">
+    <row r="122" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="4">
         <v>45915</v>
       </c>
       <c r="B122" t="s">
@@ -2551,32 +2574,32 @@
       <c r="C122" s="5">
         <v>-20</v>
       </c>
-      <c r="D122" s="2">
+      <c r="D122" s="6">
         <v>43.99</v>
       </c>
-      <c r="E122" s="2">
+      <c r="E122" s="6">
         <v>0.41</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A123" s="1">
+    <row r="123" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="4">
         <v>45915</v>
       </c>
       <c r="B123" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C123" s="5">
         <v>7</v>
       </c>
-      <c r="D123" s="2">
+      <c r="D123" s="6">
         <v>336.31</v>
       </c>
-      <c r="E123" s="2">
+      <c r="E123" s="6">
         <v>0.39</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A124" s="1">
+    <row r="124" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="4">
         <v>45915</v>
       </c>
       <c r="B124" t="s">
@@ -2585,15 +2608,15 @@
       <c r="C124" s="5">
         <v>25</v>
       </c>
-      <c r="D124" s="2">
+      <c r="D124" s="6">
         <v>112.23</v>
       </c>
-      <c r="E124" s="2">
+      <c r="E124" s="6">
         <v>0.4</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A125" s="1">
+    <row r="125" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="4">
         <v>45915</v>
       </c>
       <c r="B125" t="s">
@@ -2602,15 +2625,15 @@
       <c r="C125" s="5">
         <v>12</v>
       </c>
-      <c r="D125" s="2">
+      <c r="D125" s="6">
         <v>52.58</v>
       </c>
-      <c r="E125" s="2">
+      <c r="E125" s="6">
         <v>0.39</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A126" s="1">
+    <row r="126" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="4">
         <v>45915</v>
       </c>
       <c r="B126" t="s">
@@ -2619,32 +2642,32 @@
       <c r="C126" s="5">
         <v>-17</v>
       </c>
-      <c r="D126" s="2">
+      <c r="D126" s="6">
         <v>65.33</v>
       </c>
-      <c r="E126" s="2">
+      <c r="E126" s="6">
         <v>0.42</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A127" s="1">
+    <row r="127" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="4">
         <v>45915</v>
       </c>
       <c r="B127" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C127" s="5">
         <v>-8</v>
       </c>
-      <c r="D127" s="2">
+      <c r="D127" s="6">
         <v>90.15</v>
       </c>
-      <c r="E127" s="2">
+      <c r="E127" s="6">
         <v>0.4</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A128" s="1">
+    <row r="128" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="4">
         <v>45915</v>
       </c>
       <c r="B128" t="s">
@@ -2653,32 +2676,32 @@
       <c r="C128" s="5">
         <v>-6</v>
       </c>
-      <c r="D128" s="2">
+      <c r="D128" s="6">
         <v>108.18</v>
       </c>
-      <c r="E128" s="2">
+      <c r="E128" s="6">
         <v>0.39</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A129" s="1">
+    <row r="129" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="4">
         <v>45922</v>
       </c>
       <c r="B129" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C129" s="5">
         <v>-8</v>
       </c>
-      <c r="D129" s="2">
+      <c r="D129" s="6">
         <v>49.22</v>
       </c>
-      <c r="E129" s="2">
+      <c r="E129" s="6">
         <v>0.39</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A130" s="1">
+    <row r="130" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="4">
         <v>45922</v>
       </c>
       <c r="B130" t="s">
@@ -2687,15 +2710,15 @@
       <c r="C130" s="5">
         <v>-7</v>
       </c>
-      <c r="D130" s="2">
+      <c r="D130" s="6">
         <v>110.1</v>
       </c>
-      <c r="E130" s="2">
+      <c r="E130" s="6">
         <v>0.39</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A131" s="1">
+    <row r="131" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="4">
         <v>45922</v>
       </c>
       <c r="B131" t="s">
@@ -2704,15 +2727,15 @@
       <c r="C131" s="5">
         <v>-32</v>
       </c>
-      <c r="D131" s="2">
+      <c r="D131" s="6">
         <v>53.06</v>
       </c>
-      <c r="E131" s="2">
+      <c r="E131" s="6">
         <v>0.41</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A132" s="1">
+    <row r="132" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="4">
         <v>45922</v>
       </c>
       <c r="B132" t="s">
@@ -2721,15 +2744,15 @@
       <c r="C132" s="5">
         <v>-12</v>
       </c>
-      <c r="D132" s="2">
+      <c r="D132" s="6">
         <v>45.94</v>
       </c>
-      <c r="E132" s="2">
+      <c r="E132" s="6">
         <v>0.4</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A133" s="1">
+    <row r="133" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="4">
         <v>45922</v>
       </c>
       <c r="B133" t="s">
@@ -2738,32 +2761,32 @@
       <c r="C133" s="5">
         <v>3</v>
       </c>
-      <c r="D133" s="2">
+      <c r="D133" s="6">
         <v>515.88</v>
       </c>
-      <c r="E133" s="2">
+      <c r="E133" s="6">
         <v>0.39</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A134" s="1">
+    <row r="134" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="4">
         <v>45923</v>
       </c>
       <c r="B134" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C134" s="5">
         <v>5</v>
       </c>
-      <c r="D134" s="2">
+      <c r="D134" s="6">
         <v>347.91</v>
       </c>
-      <c r="E134" s="2">
+      <c r="E134" s="6">
         <v>0.38</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A135" s="1">
+    <row r="135" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="4">
         <v>45923</v>
       </c>
       <c r="B135" t="s">
@@ -2772,15 +2795,15 @@
       <c r="C135" s="5">
         <v>4</v>
       </c>
-      <c r="D135" s="2">
+      <c r="D135" s="6">
         <v>715.21</v>
       </c>
-      <c r="E135" s="2">
+      <c r="E135" s="6">
         <v>1.85</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A136" s="1">
+    <row r="136" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="4">
         <v>45929</v>
       </c>
       <c r="B136" t="s">
@@ -2789,15 +2812,15 @@
       <c r="C136" s="5">
         <v>8</v>
       </c>
-      <c r="D136" s="2">
+      <c r="D136" s="6">
         <v>128.72</v>
       </c>
-      <c r="E136" s="2">
+      <c r="E136" s="6">
         <v>0.38</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A137" s="1">
+    <row r="137" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="4">
         <v>45929</v>
       </c>
       <c r="B137" t="s">
@@ -2806,15 +2829,15 @@
       <c r="C137" s="5">
         <v>-25</v>
       </c>
-      <c r="D137" s="2">
+      <c r="D137" s="6">
         <v>64.37</v>
       </c>
-      <c r="E137" s="2">
+      <c r="E137" s="6">
         <v>0.41</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A138" s="1">
+    <row r="138" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="4">
         <v>45929</v>
       </c>
       <c r="B138" t="s">
@@ -2823,15 +2846,15 @@
       <c r="C138" s="5">
         <v>-4</v>
       </c>
-      <c r="D138" s="2">
+      <c r="D138" s="6">
         <v>183.17</v>
       </c>
-      <c r="E138" s="2">
+      <c r="E138" s="6">
         <v>0.38</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A139" s="1">
+    <row r="139" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="4">
         <v>45929</v>
       </c>
       <c r="B139" t="s">
@@ -2840,15 +2863,15 @@
       <c r="C139" s="5">
         <v>-17</v>
       </c>
-      <c r="D139" s="2">
+      <c r="D139" s="6">
         <v>38.380000000000003</v>
       </c>
-      <c r="E139" s="2">
+      <c r="E139" s="6">
         <v>0.38</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A140" s="1">
+    <row r="140" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="4">
         <v>45929</v>
       </c>
       <c r="B140" t="s">
@@ -2857,32 +2880,32 @@
       <c r="C140" s="5">
         <v>89</v>
       </c>
-      <c r="D140" s="2">
+      <c r="D140" s="6">
         <v>101.25</v>
       </c>
-      <c r="E140" s="2">
+      <c r="E140" s="6">
         <v>0.45</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A141" s="1">
+    <row r="141" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="4">
         <v>45929</v>
       </c>
       <c r="B141" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C141" s="5">
         <v>-24</v>
       </c>
-      <c r="D141" s="2">
+      <c r="D141" s="6">
         <v>89.31</v>
       </c>
-      <c r="E141" s="2">
+      <c r="E141" s="6">
         <v>0.43</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A142" s="1">
+    <row r="142" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="4">
         <v>45929</v>
       </c>
       <c r="B142" t="s">
@@ -2891,15 +2914,15 @@
       <c r="C142" s="5">
         <v>-6</v>
       </c>
-      <c r="D142" s="2">
+      <c r="D142" s="6">
         <v>43.39</v>
       </c>
-      <c r="E142" s="2">
+      <c r="E142" s="6">
         <v>0.39</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A143" s="1">
+    <row r="143" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="4">
         <v>45929</v>
       </c>
       <c r="B143" t="s">
@@ -2908,49 +2931,49 @@
       <c r="C143" s="5">
         <v>-61</v>
       </c>
-      <c r="D143" s="2">
+      <c r="D143" s="6">
         <v>111.46</v>
       </c>
-      <c r="E143" s="2">
+      <c r="E143" s="6">
         <v>0.44</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A144" s="1">
+    <row r="144" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="4">
         <v>45929</v>
       </c>
       <c r="B144" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C144" s="5">
         <v>13</v>
       </c>
-      <c r="D144" s="2">
+      <c r="D144" s="6">
         <v>664.34</v>
       </c>
-      <c r="E144" s="2">
+      <c r="E144" s="6">
         <v>0.39</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A145" s="1">
+    <row r="145" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="4">
         <v>45929</v>
       </c>
       <c r="B145" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C145" s="5">
         <v>-5</v>
       </c>
-      <c r="D145" s="2">
+      <c r="D145" s="6">
         <v>351.8</v>
       </c>
-      <c r="E145" s="2">
+      <c r="E145" s="6">
         <v>0.39</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A146" s="1">
+    <row r="146" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="4">
         <v>45929</v>
       </c>
       <c r="B146" t="s">
@@ -2959,15 +2982,15 @@
       <c r="C146" s="5">
         <v>116</v>
       </c>
-      <c r="D146" s="2">
+      <c r="D146" s="6">
         <v>110.68</v>
       </c>
-      <c r="E146" s="2">
+      <c r="E146" s="6">
         <v>0.53</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A147" s="1">
+    <row r="147" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="4">
         <v>45929</v>
       </c>
       <c r="B147" t="s">
@@ -2976,15 +2999,15 @@
       <c r="C147" s="5">
         <v>-21</v>
       </c>
-      <c r="D147" s="2">
+      <c r="D147" s="6">
         <v>53.24</v>
       </c>
-      <c r="E147" s="2">
+      <c r="E147" s="6">
         <v>0.4</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A148" s="1">
+    <row r="148" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="4">
         <v>45929</v>
       </c>
       <c r="B148" t="s">
@@ -2993,15 +3016,15 @@
       <c r="C148" s="5">
         <v>-9</v>
       </c>
-      <c r="D148" s="2">
+      <c r="D148" s="6">
         <v>63.74</v>
       </c>
-      <c r="E148" s="2">
+      <c r="E148" s="6">
         <v>0.4</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A149" s="1">
+    <row r="149" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="4">
         <v>45929</v>
       </c>
       <c r="B149" t="s">
@@ -3010,15 +3033,15 @@
       <c r="C149" s="5">
         <v>-11</v>
       </c>
-      <c r="D149" s="2">
+      <c r="D149" s="6">
         <v>712.91</v>
       </c>
-      <c r="E149" s="2">
+      <c r="E149" s="6">
         <v>4.3600000000000003</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A150" s="1">
+    <row r="150" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="4">
         <v>45943</v>
       </c>
       <c r="B150" t="s">
@@ -3027,15 +3050,15 @@
       <c r="C150" s="5">
         <v>20</v>
       </c>
-      <c r="D150" s="2">
+      <c r="D150" s="6">
         <v>31.05</v>
       </c>
-      <c r="E150" s="2">
+      <c r="E150" s="6">
         <v>0.42</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A151" s="1">
+    <row r="151" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="4">
         <v>45943</v>
       </c>
       <c r="B151" t="s">
@@ -3044,32 +3067,32 @@
       <c r="C151" s="5">
         <v>-14</v>
       </c>
-      <c r="D151" s="2">
+      <c r="D151" s="6">
         <v>122.59</v>
       </c>
-      <c r="E151" s="2">
+      <c r="E151" s="6">
         <v>0.4</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A152" s="1">
+    <row r="152" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="4">
         <v>45943</v>
       </c>
       <c r="B152" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C152" s="5">
         <v>16</v>
       </c>
-      <c r="D152" s="2">
+      <c r="D152" s="6">
         <v>90.28</v>
       </c>
-      <c r="E152" s="2">
+      <c r="E152" s="6">
         <v>0.41</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A153" s="1">
+    <row r="153" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="4">
         <v>45943</v>
       </c>
       <c r="B153" t="s">
@@ -3078,32 +3101,32 @@
       <c r="C153" s="5">
         <v>-28</v>
       </c>
-      <c r="D153" s="2">
+      <c r="D153" s="6">
         <v>53.44</v>
       </c>
-      <c r="E153" s="2">
+      <c r="E153" s="6">
         <v>0.41</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A154" s="1">
+    <row r="154" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A154" s="4">
         <v>45943</v>
       </c>
       <c r="B154" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C154" s="5">
         <v>-8</v>
       </c>
-      <c r="D154" s="2">
+      <c r="D154" s="6">
         <v>376.5</v>
       </c>
-      <c r="E154" s="2">
+      <c r="E154" s="6">
         <v>0.39</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A155" s="1">
+    <row r="155" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="4">
         <v>45943</v>
       </c>
       <c r="B155" t="s">
@@ -3112,15 +3135,15 @@
       <c r="C155" s="5">
         <v>-3</v>
       </c>
-      <c r="D155" s="2">
+      <c r="D155" s="6">
         <v>414.76</v>
       </c>
-      <c r="E155" s="2">
+      <c r="E155" s="6">
         <v>0.38</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A156" s="1">
+    <row r="156" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A156" s="4">
         <v>45943</v>
       </c>
       <c r="B156" t="s">
@@ -3129,15 +3152,15 @@
       <c r="C156" s="5">
         <v>9</v>
       </c>
-      <c r="D156" s="2">
+      <c r="D156" s="6">
         <v>108.04</v>
       </c>
-      <c r="E156" s="2">
+      <c r="E156" s="6">
         <v>0.39</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A157" s="1">
+    <row r="157" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A157" s="4">
         <v>45943</v>
       </c>
       <c r="B157" t="s">
@@ -3146,15 +3169,15 @@
       <c r="C157" s="5">
         <v>20</v>
       </c>
-      <c r="D157" s="2">
+      <c r="D157" s="6">
         <v>111.4</v>
       </c>
-      <c r="E157" s="2">
+      <c r="E157" s="6">
         <v>0.4</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A158" s="1">
+    <row r="158" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A158" s="4">
         <v>45943</v>
       </c>
       <c r="B158" t="s">
@@ -3163,19 +3186,405 @@
       <c r="C158" s="5">
         <v>-6</v>
       </c>
-      <c r="D158" s="2">
+      <c r="D158" s="6">
         <v>710.59</v>
       </c>
-      <c r="E158" s="2">
+      <c r="E158" s="6">
         <v>2.41</v>
       </c>
     </row>
+    <row r="159" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="4">
+        <v>45950</v>
+      </c>
+      <c r="B159" t="s">
+        <v>6</v>
+      </c>
+      <c r="C159" s="5">
+        <v>1</v>
+      </c>
+      <c r="D159" s="6">
+        <v>667.34</v>
+      </c>
+      <c r="E159" s="6">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="4">
+        <v>45950</v>
+      </c>
+      <c r="B160" t="s">
+        <v>32</v>
+      </c>
+      <c r="C160" s="5">
+        <v>-6</v>
+      </c>
+      <c r="D160" s="6">
+        <v>142.79</v>
+      </c>
+      <c r="E160" s="6">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A161" s="4">
+        <v>45953</v>
+      </c>
+      <c r="B161" t="s">
+        <v>5</v>
+      </c>
+      <c r="C161" s="5">
+        <v>1540.12</v>
+      </c>
+      <c r="D161" s="6">
+        <v>1</v>
+      </c>
+      <c r="E161" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A162" s="4">
+        <v>45957</v>
+      </c>
+      <c r="B162" t="s">
+        <v>32</v>
+      </c>
+      <c r="C162" s="5">
+        <v>-30</v>
+      </c>
+      <c r="D162" s="6">
+        <v>113.5</v>
+      </c>
+      <c r="E162" s="6">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="4">
+        <v>45957</v>
+      </c>
+      <c r="B163" t="s">
+        <v>27</v>
+      </c>
+      <c r="C163" s="5">
+        <v>-8</v>
+      </c>
+      <c r="D163" s="6">
+        <v>145</v>
+      </c>
+      <c r="E163" s="6">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="4">
+        <v>45957</v>
+      </c>
+      <c r="B164" t="s">
+        <v>29</v>
+      </c>
+      <c r="C164" s="5">
+        <v>1</v>
+      </c>
+      <c r="D164" s="6">
+        <v>265.14</v>
+      </c>
+      <c r="E164" s="6">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A165" s="4">
+        <v>45957</v>
+      </c>
+      <c r="B165" t="s">
+        <v>33</v>
+      </c>
+      <c r="C165" s="5">
+        <v>12</v>
+      </c>
+      <c r="D165" s="6">
+        <v>31.5</v>
+      </c>
+      <c r="E165" s="6">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="4">
+        <v>45957</v>
+      </c>
+      <c r="B166" t="s">
+        <v>7</v>
+      </c>
+      <c r="C166" s="5">
+        <v>-5</v>
+      </c>
+      <c r="D166" s="6">
+        <v>371.01</v>
+      </c>
+      <c r="E166" s="6">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="4">
+        <v>45957</v>
+      </c>
+      <c r="B167" t="s">
+        <v>20</v>
+      </c>
+      <c r="C167" s="5">
+        <v>-6</v>
+      </c>
+      <c r="D167" s="6">
+        <v>118.66</v>
+      </c>
+      <c r="E167" s="6">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A168" s="4">
+        <v>45957</v>
+      </c>
+      <c r="B168" t="s">
+        <v>15</v>
+      </c>
+      <c r="C168" s="5">
+        <v>10</v>
+      </c>
+      <c r="D168" s="6">
+        <v>112.71</v>
+      </c>
+      <c r="E168" s="6">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A169" s="4">
+        <v>45957</v>
+      </c>
+      <c r="B169" t="s">
+        <v>23</v>
+      </c>
+      <c r="C169" s="5">
+        <v>1</v>
+      </c>
+      <c r="D169" s="6">
+        <v>732.48</v>
+      </c>
+      <c r="E169" s="6">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A170" s="4">
+        <v>45957</v>
+      </c>
+      <c r="B170" t="s">
+        <v>8</v>
+      </c>
+      <c r="C170" s="5">
+        <v>45</v>
+      </c>
+      <c r="D170" s="6">
+        <v>110.45</v>
+      </c>
+      <c r="E170" s="6">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A171" s="1">
+        <v>46008</v>
+      </c>
+      <c r="B171" t="s">
+        <v>5</v>
+      </c>
+      <c r="C171" s="2">
+        <v>5034.38</v>
+      </c>
+      <c r="D171" s="3">
+        <v>1</v>
+      </c>
+      <c r="E171" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A172" s="1">
+        <v>46008</v>
+      </c>
+      <c r="B172" t="s">
+        <v>8</v>
+      </c>
+      <c r="C172" s="2">
+        <v>-45</v>
+      </c>
+      <c r="D172" s="3">
+        <v>110.33</v>
+      </c>
+      <c r="E172" s="3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A173" s="1">
+        <v>46008</v>
+      </c>
+      <c r="B173" t="s">
+        <v>23</v>
+      </c>
+      <c r="C173" s="2">
+        <v>3</v>
+      </c>
+      <c r="D173" s="3">
+        <v>729.41</v>
+      </c>
+      <c r="E173" s="3">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A174" s="1">
+        <v>46008</v>
+      </c>
+      <c r="B174" t="s">
+        <v>29</v>
+      </c>
+      <c r="C174" s="2">
+        <v>6</v>
+      </c>
+      <c r="D174" s="3">
+        <v>306.12</v>
+      </c>
+      <c r="E174" s="3">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A175" s="1">
+        <v>46008</v>
+      </c>
+      <c r="B175" t="s">
+        <v>7</v>
+      </c>
+      <c r="C175" s="2">
+        <v>5</v>
+      </c>
+      <c r="D175" s="3">
+        <v>398.82</v>
+      </c>
+      <c r="E175" s="3">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A176" s="1">
+        <v>46008</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" s="2">
+        <v>40</v>
+      </c>
+      <c r="D176" s="3">
+        <v>53.26</v>
+      </c>
+      <c r="E176" s="3">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A177" s="1">
+        <v>46008</v>
+      </c>
+      <c r="B177" t="s">
+        <v>15</v>
+      </c>
+      <c r="C177" s="2">
+        <v>-91</v>
+      </c>
+      <c r="D177" s="3">
+        <v>110.45</v>
+      </c>
+      <c r="E177" s="3">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A178" s="1">
+        <v>46008</v>
+      </c>
+      <c r="B178" t="s">
+        <v>29</v>
+      </c>
+      <c r="C178" s="2">
+        <v>15</v>
+      </c>
+      <c r="D178" s="3">
+        <v>303.18</v>
+      </c>
+      <c r="E178" s="3">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A179" s="1">
+        <v>46008</v>
+      </c>
+      <c r="B179" t="s">
+        <v>32</v>
+      </c>
+      <c r="C179" s="2">
+        <v>20</v>
+      </c>
+      <c r="D179" s="3">
+        <v>135.59</v>
+      </c>
+      <c r="E179" s="3">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A180" s="1">
+        <v>46008</v>
+      </c>
+      <c r="B180" t="s">
+        <v>11</v>
+      </c>
+      <c r="C180" s="2">
+        <v>50</v>
+      </c>
+      <c r="D180" s="3">
+        <v>44.48</v>
+      </c>
+      <c r="E180" s="3">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A181" s="1">
+        <v>46008</v>
+      </c>
+      <c r="B181" t="s">
+        <v>23</v>
+      </c>
+      <c r="C181" s="2">
+        <v>6</v>
+      </c>
+      <c r="D181" s="3">
+        <v>728.47</v>
+      </c>
+      <c r="E181" s="3">
+        <v>2.56</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E97" xr:uid="{1EBC9900-0457-4E2A-A65B-407C2F1035D0}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E24">
-      <sortCondition ref="A1:A24"/>
-    </sortState>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/portfolio_tracker.xlsx
+++ b/portfolio_tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexr\AlgoTester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF364B9-B739-4C6F-B6F9-5400657D7BD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56D09D15-0EE4-48E8-A7B9-213B3EB45E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="35">
   <si>
     <t>date</t>
   </si>
@@ -125,6 +125,9 @@
   </si>
   <si>
     <t>ETHA</t>
+  </si>
+  <si>
+    <t>CHA</t>
   </si>
 </sst>
 </file>
@@ -496,7 +499,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H181"/>
+  <dimension ref="A1:H184"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
@@ -3584,6 +3587,57 @@
         <v>2.56</v>
       </c>
     </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A182" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B182" t="s">
+        <v>34</v>
+      </c>
+      <c r="C182" s="2">
+        <v>100</v>
+      </c>
+      <c r="D182" s="3">
+        <v>13.28</v>
+      </c>
+      <c r="E182" s="3">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A183" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B183" t="s">
+        <v>32</v>
+      </c>
+      <c r="C183" s="2">
+        <v>-19</v>
+      </c>
+      <c r="D183" s="3">
+        <v>156.11000000000001</v>
+      </c>
+      <c r="E183" s="3">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A184" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B184" t="s">
+        <v>7</v>
+      </c>
+      <c r="C184" s="2">
+        <v>7</v>
+      </c>
+      <c r="D184" s="3">
+        <v>421.77</v>
+      </c>
+      <c r="E184" s="3">
+        <v>0.36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
